--- a/docs/Mau_Bao_Cao_Va_Data_Mapping_QLDA.xlsx
+++ b/docs/Mau_Bao_Cao_Va_Data_Mapping_QLDA.xlsx
@@ -88,6 +88,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="00B91C1C"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00047857"/>
       <sz val="9"/>
     </font>
@@ -95,12 +101,6 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="00B45309"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="00B91C1C"/>
       <sz val="9"/>
     </font>
     <font>
@@ -140,7 +140,7 @@
       <sz val="8"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="18">
     <fill>
       <patternFill/>
     </fill>
@@ -167,20 +167,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-        <bgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEF9C3"/>
-        <bgColor rgb="00FEF9C3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FEE2E2"/>
-        <bgColor rgb="00FEE2E2"/>
+        <fgColor rgb="00E2E8F0"/>
+        <bgColor rgb="00E2E8F0"/>
       </patternFill>
     </fill>
     <fill>
@@ -245,8 +233,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2E8F0"/>
-        <bgColor rgb="00E2E8F0"/>
+        <fgColor rgb="00DCFCE7"/>
+        <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+        <bgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
   </fills>
@@ -276,7 +270,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -320,18 +314,26 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -340,9 +342,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -357,15 +356,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -377,8 +375,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -758,12 +755,12 @@
   <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="29" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -776,7 +773,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TỔNG HỢP BIỂU MẪU BÁO CÁO THỰC TẾ &amp; MÔ TẢ DATA MAPPING NGUỒN CSDL</t>
+          <t>TỔNG HỢP BIỂU MẪU BÁO CÁO THỰC TẾ &amp; MÔ TẢ DATA MAPPING NGUỒN CSDL (CẬP NHẬT THEO HỆ THỐNG ĐANG CHẠY)</t>
         </is>
       </c>
     </row>
@@ -791,7 +788,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>DANH SÁCH BIỂU MẪU BÁO CÁO &amp; MÔ TẢ ĐÃ CẬP NHẬT THEO THỰC TẾ DỰ ÁN</t>
+          <t>DANH SÁCH BIỂU MẪU BÁO CÁO &amp; MÔ TẢ ĐÃ ĐỒNG BỘ THEO THỰC TẾ PHẦN MỀM</t>
         </is>
       </c>
     </row>
@@ -823,7 +820,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Trạng Thái Cập Nhật</t>
+          <t>Trạng Thái Thực Tế Phần Mềm</t>
         </is>
       </c>
     </row>
@@ -833,12 +830,12 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Báo cáo 1 - Tiến độ dự án</t>
+          <t>Báo cáo 1: Tiến độ Dự án triển khai</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
         <is>
-          <t>Theo dõi tiến độ triển khai, thời gian bắt đầu/kết thúc, số ngày còn lại và cảnh báo rủi ro (RAG) theo thời gian</t>
+          <t>Theo dõi tiến độ triển khai, thời gian bắt đầu/kết thúc, số ngày còn lại và trạng thái thực tế của các dự án</t>
         </is>
       </c>
       <c r="D7" s="8" t="inlineStr">
@@ -853,7 +850,7 @@
       </c>
       <c r="F7" s="9" t="inlineStr">
         <is>
-          <t>Đã cập nhật bộ lọc &amp; RAG</t>
+          <t>Chuẩn 11 cột thực tế (đã bỏ cột rủi ro RAG)</t>
         </is>
       </c>
     </row>
@@ -883,7 +880,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Đã hiển thị cột phân kỳ động, bỏ VNĐ</t>
+          <t>Đã hiển thị cột phân kỳ động, bỏ chữ VNĐ</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1030,7 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Chuẩn hóa prefix DAN, GT, HD, TT, NT, NV, LDA, LHD</t>
+          <t>Đồng bộ danh mục theo ProductionSeeder</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1045,7 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>1. Mỗi sheet biểu mẫu gồm 3 phần: [1] Bộ lọc &amp; Tiêu chí tra cứu; [2] Biểu mẫu dữ liệu mẫu; [3] Bảng mô tả chi tiết nguồn dữ liệu (Data Mapping từ CSDL / Backend Entity).</t>
+          <t>1. Mỗi sheet biểu mẫu gồm 3 phần: [1] Bộ lọc &amp; Tiêu chí tra cứu; [2] Biểu mẫu dữ liệu mẫu khớp 100% giao diện thực tế phần mềm; [3] Bảng mô tả chi tiết nguồn dữ liệu (Data Mapping từ CSDL / Backend Entity).</t>
         </is>
       </c>
     </row>
@@ -1073,33 +1070,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="27" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>BÁO CÁO 1 - TIẾN ĐỘ DỰ ÁN</t>
+          <t>Báo cáo 1: Tiến độ Dự án triển khai</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Theo dõi tiến độ tổng thể, mốc thời gian, trạng thái và mức độ cảnh báo rủi ro (RAG) của các dự án</t>
+          <t>Theo dõi tiến độ triển khai thực tế, đơn vị chủ trì, PM phụ trách, thời hạn và trạng thái của các dự án (Khớp 100% UI phần mềm)</t>
         </is>
       </c>
     </row>
@@ -1226,64 +1223,64 @@
     <row r="12">
       <c r="A12" s="19" t="inlineStr">
         <is>
-          <t>2. BIỂU MẪU DỮ LIỆU CHI TIẾT (REPORT DATA PREVIEW)</t>
+          <t>2. BIỂU MẪU DỮ LIỆU CHI TIẾT (REPORT DATA PREVIEW - Khớp thực tế UI phần mềm)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
-          <t>STT</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Mã dự án</t>
+          <t>MÃ DỰ ÁN</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>Đơn vị chủ trì</t>
+          <t>TÊN DỰ ÁN TRIỂN KHAI</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>PM phụ trách</t>
+          <t>ĐƠN VỊ CHỦ TRÌ</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Loại dự án</t>
+          <t>PM PHỤ TRÁCH</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu</t>
+          <t>LOẠI DỰ ÁN</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Ngày kết thúc</t>
+          <t>NGÀY BẮT ĐẦU</t>
         </is>
       </c>
       <c r="H13" s="5" t="inlineStr">
         <is>
-          <t>Tiến độ (%)</t>
+          <t>NGÀY KẾT THÚC</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Thời gian còn lại (ngày)</t>
+          <t>TIẾN ĐỘ</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Trạng thái thực tế</t>
+          <t>THỜI GIAN CÒN LẠI (NGÀY)</t>
         </is>
       </c>
       <c r="K13" s="5" t="inlineStr">
         <is>
-          <t>Cảnh báo rủi ro (RAG)</t>
+          <t>TRẠNG THÁI THỰC TẾ</t>
         </is>
       </c>
     </row>
@@ -1293,50 +1290,36 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>DAN-2026-001</t>
+          <t>DAN-2026-859</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>Trung tâm CNTT</t>
+          <t>Test trạng thái</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>Nguyễn Văn A</t>
+          <t>TT CNTT</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>Bản quyền phần mềm</t>
-        </is>
-      </c>
-      <c r="F14" s="9" t="inlineStr">
-        <is>
-          <t>09/08/2026</t>
-        </is>
-      </c>
-      <c r="G14" s="9" t="inlineStr">
-        <is>
-          <t>12/12/2026</t>
-        </is>
-      </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>10%</t>
-        </is>
-      </c>
-      <c r="I14" s="9" t="n">
-        <v>95</v>
-      </c>
-      <c r="J14" s="9" t="inlineStr">
-        <is>
-          <t>Đang triển khai</t>
-        </is>
-      </c>
-      <c r="K14" s="21" t="inlineStr">
-        <is>
-          <t>🟢 Đúng tiến độ</t>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Ngân hàng số &amp; Thẻ</t>
+        </is>
+      </c>
+      <c r="G14" s="9" t="inlineStr"/>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr"/>
+      <c r="K14" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
         </is>
       </c>
     </row>
@@ -1346,50 +1329,36 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>DAN-2026-002</t>
+          <t>DAN-2026-595</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>Trung tâm CNTT</t>
+          <t>Dự án Hợp nhất (Gộp từ DAN-2026-879 &amp; DAN-2026-503)</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Trần Thị B</t>
+          <t>TT CNTT</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Mua sắm phần cứng</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
-        <is>
-          <t>30/06/2026</t>
-        </is>
-      </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="9" t="inlineStr">
-        <is>
-          <t>Đã hoàn thành</t>
-        </is>
-      </c>
-      <c r="K15" s="21" t="inlineStr">
-        <is>
-          <t>🟢 Hoàn thành</t>
+          <t>Lê Thị Ánh</t>
+        </is>
+      </c>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>Hạ tầng</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
         </is>
       </c>
     </row>
@@ -1399,50 +1368,32 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>DAN-2026-003</t>
+          <t>DAN-TEST-NV-593</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Phòng Kế toán</t>
+          <t>Dự án kiểm tra 2 nguồn vốn cùng năm</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>Lê Văn C</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>Tư vấn</t>
-        </is>
-      </c>
-      <c r="F16" s="9" t="inlineStr">
-        <is>
-          <t>15/03/2026</t>
-        </is>
-      </c>
-      <c r="G16" s="9" t="inlineStr">
-        <is>
-          <t>15/10/2026</t>
-        </is>
-      </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="I16" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="J16" s="9" t="inlineStr">
-        <is>
-          <t>Đang triển khai</t>
-        </is>
-      </c>
-      <c r="K16" s="22" t="inlineStr">
-        <is>
-          <t>🟡 Nguy cơ chậm</t>
+          <t>TT CNTT</t>
+        </is>
+      </c>
+      <c r="E16" s="8" t="inlineStr"/>
+      <c r="F16" s="8" t="inlineStr">
+        <is>
+          <t>Hạ tầng</t>
+        </is>
+      </c>
+      <c r="G16" s="9" t="inlineStr"/>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr"/>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
         </is>
       </c>
     </row>
@@ -1452,251 +1403,269 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>DAN-2026-004</t>
+          <t>DAN-2026-744</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
+          <t>Mua sắm Switch</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>CNTT</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F17" s="8" t="inlineStr">
+        <is>
+          <t>Hạ tầng</t>
+        </is>
+      </c>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>08/06/2023</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr"/>
+      <c r="J17" s="9" t="inlineStr"/>
+      <c r="K17" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>DAN-2026-214</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>Nâng cấp Hệ thống QLTT báo cáo Quỹ tín dụng nhân dân (PRMS)</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
           <t>Trung tâm CNTT</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Phạm Văn D</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>Bảo trì</t>
-        </is>
-      </c>
-      <c r="F17" s="9" t="inlineStr">
-        <is>
-          <t>01/02/2026</t>
-        </is>
-      </c>
-      <c r="G17" s="9" t="inlineStr">
-        <is>
-          <t>01/08/2026</t>
-        </is>
-      </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="I17" s="9" t="n">
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Bảo trì</t>
+        </is>
+      </c>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
+        <is>
+          <t>17/07/2026</t>
+        </is>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="9" t="inlineStr">
-        <is>
-          <t>Đang triển khai</t>
-        </is>
-      </c>
-      <c r="K17" s="23" t="inlineStr">
-        <is>
-          <t>🔴 Quá hạn</t>
-        </is>
-      </c>
-    </row>
-    <row r="18"/>
-    <row r="19"/>
+      <c r="K18" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>DAN-2026-232</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr">
+        <is>
+          <t>Test thông báo Email</t>
+        </is>
+      </c>
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>TT CNTT</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>Phạm Huy Nhất</t>
+        </is>
+      </c>
+      <c r="F19" s="8" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Bảo trì</t>
+        </is>
+      </c>
+      <c r="G19" s="9" t="inlineStr"/>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr"/>
+      <c r="K19" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
-        <is>
-          <t>3. MÔ TẢ CHI TIẾT NGUỒN DỮ LIỆU &amp; LOGIC TÍNH TOÁN (DATA MAPPING)</t>
+      <c r="A20" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>DAN-2026-503</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>Test gộp 01</t>
+        </is>
+      </c>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>TT CNTT</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>Xây dựng &amp; Bảo trì</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr"/>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr"/>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>Chuẩn bị đầu tư</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="25" t="inlineStr">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="23" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="23" t="n"/>
+      <c r="H21" s="23" t="n"/>
+      <c r="I21" s="23" t="n"/>
+      <c r="J21" s="23" t="n"/>
+      <c r="K21" s="23" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="24" t="inlineStr">
+        <is>
+          <t>3. MÔ TẢ CHI TIẾT NGUỒN DỮ LIỆU &amp; LOGIC TÍNH TOÁN (DATA MAPPING - Chuẩn 11 cột thực tế)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B21" s="25" t="inlineStr">
-        <is>
-          <t>Tên Cột Hiển Thị</t>
-        </is>
-      </c>
-      <c r="C21" s="25" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Tên Cột Hiển Thị Trên UI</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="inlineStr">
         <is>
           <t>Bảng / Entity Nguồn</t>
         </is>
       </c>
-      <c r="D21" s="25" t="inlineStr">
+      <c r="D25" s="25" t="inlineStr">
         <is>
           <t>Trường Dữ Liệu (Field)</t>
         </is>
       </c>
-      <c r="E21" s="25" t="inlineStr">
+      <c r="E25" s="25" t="inlineStr">
         <is>
           <t>Kiểu Dữ Liệu</t>
         </is>
       </c>
-      <c r="F21" s="25" t="inlineStr">
+      <c r="F25" s="25" t="inlineStr">
         <is>
           <t>Logic Lấy Dữ Liệu &amp; Công Thức Tính Toán Chi Tiết</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Chương trình (System)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Index tự tăng</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Số thứ tự dòng trong báo cáo (1, 2, 3...)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Mã dự án</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>DuAn.Code</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>string (nvarchar)</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Mã định danh duy nhất của dự án. Quy chuẩn định dạng: DAN-[Năm]-[STT 3 số] (ví dụ: DAN-2026-001)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Đơn vị chủ trì</t>
-        </is>
-      </c>
-      <c r="C24" s="12" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
-        </is>
-      </c>
-      <c r="D24" s="12" t="inlineStr">
-        <is>
-          <t>DuAn.ToChucThucHien / ChuDauTu</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F24" s="12" t="inlineStr">
-        <is>
-          <t>Đơn vị hoặc phòng ban chủ trì triển khai dự án (mặc định 'Trung tâm CNTT' hoặc lấy từ trường ToChucThucHien)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>PM phụ trách</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Bảng Users (liên kết DuAns.ChuDuAnId)</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>DuAn.ChuDuAn.FullName</t>
-        </is>
-      </c>
-      <c r="E25" s="9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="inlineStr">
-        <is>
-          <t>Họ tên người quản lý/phụ trách dự án (User liên kết qua khóa ngoại ChuDuAnId hoặc CreatedByUser)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Loại dự án</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Bảng PhanLoaiDuAns (DanhMuc)</t>
+          <t>Chương trình (System)</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>DuAn.PhanLoaiDuAn.TenPhanLoai</t>
+          <t>Index tự tăng</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Loại dự án: Bảo trì, Mua sắm phần cứng, Bản quyền phần mềm, Tư vấn, Thuê dịch vụ, Khác</t>
+          <t>Số thứ tự dòng trong báo cáo (1, 2, 3...)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ngày bắt đầu</t>
+          <t>MÃ DỰ ÁN</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -1706,27 +1675,27 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>DuAn.NgayBatDau</t>
+          <t>DuAn.Code</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>string (nvarchar)</t>
         </is>
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Ngày khởi động/bắt đầu dự án theo kế hoạch phê duyệt. Format: dd/MM/yyyy</t>
+          <t>Mã định danh duy nhất của dự án. Quy chuẩn định dạng: DAN-[Năm]-[STT 3 số] (ví dụ: DAN-2026-214)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Ngày kết thúc</t>
+          <t>TÊN DỰ ÁN TRIỂN KHAI</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
@@ -1736,97 +1705,97 @@
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>DuAn.NgayKetThuc</t>
+          <t>DuAn.Name</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>DateTime?</t>
+          <t>string (nvarchar)</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Ngày dự kiến hoàn thành dự án theo kế hoạch. Format: dd/MM/yyyy</t>
+          <t>Tên đầy đủ của dự án triển khai</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Tiến độ (%)</t>
+          <t>ĐƠN VỊ CHỦ TRÌ</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Bảng CongViecGoiThaus &amp; DuAns</t>
+          <t>Bảng DuAns (Entity DuAn)</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>Tính toán hoặc DuAn.TienDoPhanTram</t>
+          <t>DuAn.ToChucThucHien / ChuDauTu</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Tỷ lệ % hoàn thành dự án. Tính từ tỷ lệ hoàn thành các công việc gói thầu có trọng số, hoặc % giải ngân thực tế</t>
+          <t>Đơn vị hoặc phòng ban chủ trì triển khai dự án (mặc định 'TT CNTT' / 'Trung tâm CNTT' hoặc lấy từ trường ToChucThucHien)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Thời gian còn lại (ngày)</t>
+          <t>PM PHỤ TRÁCH</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng Users (liên kết DuAns.ChuDuAnId)</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>(NgayKetThuc - Today).Days</t>
+          <t>DuAn.ChuDuAn.FullName</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Số ngày còn lại tính từ ngày hiện tại (Today) đến Ngày kết thúc: Math.Max(0, (NgayKetThuc.Date - DateTime.Today).Days). Nếu đã hoàn thành hoặc quá hạn thì = 0</t>
+          <t>Họ tên người quản lý/phụ trách dự án (User liên kết qua khóa ngoại ChuDuAnId hoặc CreatedByUser.FullName)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Trạng thái thực tế</t>
+          <t>LOẠI DỰ ÁN</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
+          <t>Bảng PhanLoaiDuAns (DanhMuc)</t>
         </is>
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>DuAn.TrangThai / DaKetThuc</t>
+          <t>DuAn.PhanLoaiDuAn.Name</t>
         </is>
       </c>
       <c r="E31" s="9" t="inlineStr">
@@ -1836,48 +1805,188 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>Trạng thái dự án: 1: Chưa triển khai | 2: Đang triển khai | 3: Tạm dừng | 4: Đã nghiệm thu/hoàn thành | 5: Đã hủy</t>
+          <t>Loại dự án thực tế trong hệ thống: 'Ngân hàng số &amp; Thẻ', 'Hạ tầng', 'Xây dựng &amp; Bảo trì', 'Công nghệ thông tin', 'Hệ thống phần mềm', 'Mạng &amp; An ninh bảo mật'...</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>NGÀY BẮT ĐẦU</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DuAns (Entity DuAn)</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>DuAn.NgayBatDau</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>DateTime?</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Ngày khởi động/bắt đầu dự án theo kế hoạch. Hiển thị dạng dd/MM/yyyy (để trống nếu chưa nhập)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>NGÀY KẾT THÚC</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Bảng DuAns (Entity DuAn)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>DuAn.NgayKetThuc</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>DateTime?</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Ngày dự kiến hoàn thành dự án theo kế hoạch. Hiển thị dạng dd/MM/yyyy (để trống nếu chưa nhập)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>TIẾN ĐỘ</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Bảng CongViecGoiThaus &amp; DuAns</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>Tính toán hoặc DuAn.TienDoPhanTram</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>string/decimal</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Tỷ lệ % hoàn thành dự án (ví dụ: '1%'). Tính từ tỷ lệ hoàn thành các công việc gói thầu có trọng số, hoặc % giải ngân</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>THỜI GIAN CÒN LẠI (NGÀY)</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Tính toán động</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>(NgayKetThuc - Today).Days</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>int?</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Số ngày còn lại tính từ ngày hiện tại (Today) đến Ngày kết thúc: Math.Max(0, (NgayKetThuc.Date - DateTime.Today).Days). Nếu đã đến/quá hạn hiển thị '0'</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B32" s="11" t="inlineStr">
-        <is>
-          <t>Cảnh báo rủi ro (RAG)</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="inlineStr">
-        <is>
-          <t>Hàm đánh giá rủi ro (Warning Logic)</t>
-        </is>
-      </c>
-      <c r="D32" s="12" t="inlineStr">
-        <is>
-          <t>Calculated RAG</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>TRẠNG THÁI THỰC TẾ</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DuAns (Entity DuAn)</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>DuAn.TrangThai / Enum TrangThaiDuAn</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F32" s="12" t="inlineStr">
-        <is>
-          <t>Quy tắc cảnh báo RAG: 
-- 🟢 Đúng tiến độ: Tiến độ đạt &gt;= kế hoạch hoặc còn hạn &gt; 30 ngày.
-- 🟡 Nguy cơ chậm: Còn &lt; 30 ngày nhưng tiến độ &lt; 70%, hoặc có gói thầu trễ hạn.
-- 🔴 Quá hạn / Rủi ro cao: NgayKetThuc &lt; Today mà TrangThai != 'Đã hoàn thành'.</t>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Trạng thái dự án thực tế: 'Chuẩn bị đầu tư', 'Đang triển khai', 'Nghiệm thu', 'Thanh toán', 'Quyết toán', 'Hoàn thành', 'Tạm dừng', 'Đã gộp'</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
+        <is>
+          <t>📌 GHI CHÚ ĐIỀU CHỈNH:</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="inlineStr">
+        <is>
+          <t>- Đã bổ sung cột [TÊN DỰ ÁN TRIỂN KHAI] ngay sau cột [MÃ DỰ ÁN].</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="inlineStr">
+        <is>
+          <t>- Đã xóa bỏ cột [Cảnh báo rủi ro (RAG)] để đúng 100% với thực trạng giao diện phần mềm đang có.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A20:F20"/>
+  <mergeCells count="4">
+    <mergeCell ref="A21:K21"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2306,7 +2415,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Tên Cột Hiển Thị</t>
+          <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -2689,7 +2798,7 @@
     <col width="25" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="29" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="20" customWidth="1" min="11" max="11"/>
@@ -2947,7 +3056,7 @@
       </c>
       <c r="H14" s="9" t="inlineStr">
         <is>
-          <t>Đấu thầu rộng rãi qua mạng</t>
+          <t>Đấu thầu rộng rãi</t>
         </is>
       </c>
       <c r="I14" s="9" t="inlineStr">
@@ -3087,7 +3196,7 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Chỉ định thầu rút gọn</t>
+          <t>Chỉ định thầu</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
@@ -3138,7 +3247,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Tên Cột Hiển Thị</t>
+          <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -3398,7 +3507,7 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Hình thức lựa chọn nhà thầu: Đấu thầu rộng rãi qua mạng, Chỉ định thầu, Chào hàng cạnh tranh, Mua sắm trực tiếp, Tự thực hiện...</t>
+          <t>Hình thức lựa chọn nhà thầu: Đấu thầu rộng rãi, Chỉ định thầu, Chào hàng cạnh tranh, Mua sắm trực tiếp, Tự thực hiện...</t>
         </is>
       </c>
     </row>
@@ -4030,7 +4139,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Tên Cột Hiển Thị</t>
+          <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -4711,7 +4820,7 @@
           <t>Đã nhận Thư bảo lãnh tạm ứng</t>
         </is>
       </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="I14" s="40" t="inlineStr">
         <is>
           <t>🟢 Đã thanh toán</t>
         </is>
@@ -4761,7 +4870,7 @@
           <t>Đã ký Biên bản nghiệm thu bàn giao</t>
         </is>
       </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="I15" s="41" t="inlineStr">
         <is>
           <t>🟡 Chưa thanh toán</t>
         </is>
@@ -4811,7 +4920,7 @@
           <t>Chờ hết thời hạn bảo hành</t>
         </is>
       </c>
-      <c r="I16" s="22" t="inlineStr">
+      <c r="I16" s="41" t="inlineStr">
         <is>
           <t>🟡 Chưa thanh toán</t>
         </is>
@@ -4839,7 +4948,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Tên Cột Hiển Thị</t>
+          <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -5204,19 +5313,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="40" t="inlineStr">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>NGÂN HÀNG HỢP TÁC XÃ VIỆT NAM</t>
         </is>
       </c>
-      <c r="S1" s="41" t="inlineStr">
+      <c r="S1" s="43" t="inlineStr">
         <is>
           <t>Biểu số 02.A</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="42" t="inlineStr">
         <is>
           <t>TRUNG TÂM CÔNG NGHỆ THÔNG TIN</t>
         </is>
@@ -5224,21 +5333,21 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>TÌNH HÌNH ĐẦU TƯ VÀ HUY ĐỘNG VỐN ĐỂ ĐẦU TƯ VÀO CÁC DỰ ÁN HÌNH THÀNH TSCĐ VÀ XDCB</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="43" t="inlineStr">
+      <c r="A5" s="45" t="inlineStr">
         <is>
           <t>(Ban hành kèm theo Thông tư số 200/2015/TT-BTC ngày 15/12/2015 của Bộ Tài chính)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="44" t="inlineStr">
+      <c r="A6" s="46" t="inlineStr">
         <is>
           <t>Kỳ báo cáo: Quý III năm 2026 | Đơn vị tính: Tỷ đồng</t>
         </is>
@@ -5246,231 +5355,231 @@
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="45" t="inlineStr">
+      <c r="A8" s="47" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B8" s="45" t="inlineStr">
+      <c r="B8" s="47" t="inlineStr">
         <is>
           <t>Tên dự án</t>
         </is>
       </c>
-      <c r="C8" s="45" t="inlineStr">
+      <c r="C8" s="47" t="inlineStr">
         <is>
           <t>Quyết định phê duyệt</t>
         </is>
       </c>
-      <c r="D8" s="45" t="inlineStr">
+      <c r="D8" s="47" t="inlineStr">
         <is>
           <t>Tổng mức vốn đầu tư</t>
         </is>
       </c>
-      <c r="E8" s="46" t="n"/>
-      <c r="F8" s="46" t="n"/>
-      <c r="G8" s="46" t="n"/>
-      <c r="H8" s="46" t="n"/>
-      <c r="I8" s="45" t="inlineStr">
+      <c r="E8" s="23" t="n"/>
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n"/>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="47" t="inlineStr">
         <is>
           <t>Thời gian đầu tư theo KH</t>
         </is>
       </c>
-      <c r="J8" s="45" t="inlineStr">
+      <c r="J8" s="47" t="inlineStr">
         <is>
           <t>Nguồn vốn huy động</t>
         </is>
       </c>
-      <c r="K8" s="46" t="n"/>
-      <c r="L8" s="46" t="n"/>
-      <c r="M8" s="45" t="inlineStr">
+      <c r="K8" s="23" t="n"/>
+      <c r="L8" s="23" t="n"/>
+      <c r="M8" s="47" t="inlineStr">
         <is>
           <t>Giá trị khối lượng thực hiện đến cuối kỳ</t>
         </is>
       </c>
-      <c r="N8" s="46" t="n"/>
-      <c r="O8" s="46" t="n"/>
-      <c r="P8" s="45" t="inlineStr">
+      <c r="N8" s="23" t="n"/>
+      <c r="O8" s="23" t="n"/>
+      <c r="P8" s="47" t="inlineStr">
         <is>
           <t>Giải ngân đến cuối kỳ</t>
         </is>
       </c>
-      <c r="Q8" s="46" t="n"/>
-      <c r="R8" s="46" t="n"/>
-      <c r="S8" s="45" t="inlineStr">
+      <c r="Q8" s="23" t="n"/>
+      <c r="R8" s="23" t="n"/>
+      <c r="S8" s="47" t="inlineStr">
         <is>
           <t>Giá trị tài sản đã hình thành đưa vào sử dụng</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="46" t="n"/>
-      <c r="B9" s="46" t="n"/>
-      <c r="C9" s="46" t="n"/>
-      <c r="D9" s="47" t="inlineStr">
+      <c r="A9" s="23" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="E9" s="47" t="inlineStr">
+      <c r="E9" s="48" t="inlineStr">
         <is>
           <t>Vốn CSH</t>
         </is>
       </c>
-      <c r="F9" s="47" t="inlineStr">
+      <c r="F9" s="48" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G9" s="47" t="inlineStr">
+      <c r="G9" s="48" t="inlineStr">
         <is>
           <t>Vốn vay/HĐ</t>
         </is>
       </c>
-      <c r="H9" s="47" t="inlineStr">
+      <c r="H9" s="48" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="I9" s="46" t="n"/>
-      <c r="J9" s="47" t="inlineStr">
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="48" t="inlineStr">
         <is>
           <t>Tổng số</t>
         </is>
       </c>
-      <c r="K9" s="47" t="inlineStr">
+      <c r="K9" s="48" t="inlineStr">
         <is>
           <t>Thời hạn vay</t>
         </is>
       </c>
-      <c r="L9" s="47" t="inlineStr">
+      <c r="L9" s="48" t="inlineStr">
         <is>
           <t>Lãi suất (%)</t>
         </is>
       </c>
-      <c r="M9" s="47" t="inlineStr">
+      <c r="M9" s="48" t="inlineStr">
         <is>
           <t>Kỳ trước chuyển sang</t>
         </is>
       </c>
-      <c r="N9" s="47" t="inlineStr">
+      <c r="N9" s="48" t="inlineStr">
         <is>
           <t>Thực hiện trong kỳ</t>
         </is>
       </c>
-      <c r="O9" s="47" t="inlineStr">
+      <c r="O9" s="48" t="inlineStr">
         <is>
           <t>Lũy kế đến cuối kỳ</t>
         </is>
       </c>
-      <c r="P9" s="47" t="inlineStr">
+      <c r="P9" s="48" t="inlineStr">
         <is>
           <t>Kỳ trước chuyển sang</t>
         </is>
       </c>
-      <c r="Q9" s="47" t="inlineStr">
+      <c r="Q9" s="48" t="inlineStr">
         <is>
           <t>Thực hiện trong kỳ</t>
         </is>
       </c>
-      <c r="R9" s="47" t="inlineStr">
+      <c r="R9" s="48" t="inlineStr">
         <is>
           <t>Lũy kế đến cuối kỳ</t>
         </is>
       </c>
-      <c r="S9" s="46" t="n"/>
+      <c r="S9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="48" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="B10" s="48" t="inlineStr">
+      <c r="B10" s="49" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="48" t="inlineStr">
+      <c r="C10" s="49" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D10" s="48" t="inlineStr">
+      <c r="D10" s="49" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="E10" s="48" t="inlineStr">
+      <c r="E10" s="49" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="F10" s="48" t="inlineStr">
+      <c r="F10" s="49" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="G10" s="48" t="inlineStr">
+      <c r="G10" s="49" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="H10" s="48" t="inlineStr">
+      <c r="H10" s="49" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="I10" s="48" t="inlineStr">
+      <c r="I10" s="49" t="inlineStr">
         <is>
           <t>(9)</t>
         </is>
       </c>
-      <c r="J10" s="48" t="inlineStr">
+      <c r="J10" s="49" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="K10" s="48" t="inlineStr">
+      <c r="K10" s="49" t="inlineStr">
         <is>
           <t>(11)</t>
         </is>
       </c>
-      <c r="L10" s="48" t="inlineStr">
+      <c r="L10" s="49" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="M10" s="48" t="inlineStr">
+      <c r="M10" s="49" t="inlineStr">
         <is>
           <t>(13)</t>
         </is>
       </c>
-      <c r="N10" s="48" t="inlineStr">
+      <c r="N10" s="49" t="inlineStr">
         <is>
           <t>(14)</t>
         </is>
       </c>
-      <c r="O10" s="48" t="inlineStr">
+      <c r="O10" s="49" t="inlineStr">
         <is>
           <t>(15)</t>
         </is>
       </c>
-      <c r="P10" s="48" t="inlineStr">
+      <c r="P10" s="49" t="inlineStr">
         <is>
           <t>(16)</t>
         </is>
       </c>
-      <c r="Q10" s="48" t="inlineStr">
+      <c r="Q10" s="49" t="inlineStr">
         <is>
           <t>(17)</t>
         </is>
       </c>
-      <c r="R10" s="48" t="inlineStr">
+      <c r="R10" s="49" t="inlineStr">
         <is>
           <t>(18)</t>
         </is>
       </c>
-      <c r="S10" s="48" t="inlineStr">
+      <c r="S10" s="49" t="inlineStr">
         <is>
           <t>(19)</t>
         </is>
@@ -5920,23 +6029,23 @@
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr"/>
-      <c r="D19" s="49" t="n">
+      <c r="D19" s="50" t="n">
         <v>181.89</v>
       </c>
-      <c r="E19" s="49" t="n">
+      <c r="E19" s="50" t="n">
         <v>181.89</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="49" t="n">
+      <c r="H19" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="49" t="n">
+      <c r="J19" s="50" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -5949,25 +6058,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="49" t="n">
+      <c r="M19" s="50" t="n">
         <v>2.32</v>
       </c>
-      <c r="N19" s="49" t="n">
+      <c r="N19" s="50" t="n">
         <v>48.78</v>
       </c>
-      <c r="O19" s="49" t="n">
+      <c r="O19" s="50" t="n">
         <v>51.09</v>
       </c>
-      <c r="P19" s="49" t="n">
+      <c r="P19" s="50" t="n">
         <v>2.32</v>
       </c>
-      <c r="Q19" s="49" t="n">
+      <c r="Q19" s="50" t="n">
         <v>48.78</v>
       </c>
-      <c r="R19" s="49" t="n">
+      <c r="R19" s="50" t="n">
         <v>51.09</v>
       </c>
-      <c r="S19" s="49" t="n">
+      <c r="S19" s="50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6510,23 +6619,23 @@
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
-      <c r="D29" s="49" t="n">
+      <c r="D29" s="50" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="E29" s="49" t="n">
+      <c r="E29" s="50" t="n">
         <v>72.65000000000001</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="50" t="n">
         <v>100</v>
       </c>
-      <c r="G29" s="49" t="n">
+      <c r="G29" s="50" t="n">
         <v>0</v>
       </c>
-      <c r="H29" s="49" t="n">
+      <c r="H29" s="50" t="n">
         <v>0</v>
       </c>
       <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="49" t="n">
+      <c r="J29" s="50" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="11" t="inlineStr">
@@ -6539,25 +6648,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M29" s="49" t="n">
+      <c r="M29" s="50" t="n">
         <v>23.26</v>
       </c>
-      <c r="N29" s="49" t="n">
+      <c r="N29" s="50" t="n">
         <v>21.1</v>
       </c>
-      <c r="O29" s="49" t="n">
+      <c r="O29" s="50" t="n">
         <v>44.34</v>
       </c>
-      <c r="P29" s="49" t="n">
+      <c r="P29" s="50" t="n">
         <v>23.26</v>
       </c>
-      <c r="Q29" s="49" t="n">
+      <c r="Q29" s="50" t="n">
         <v>21.1</v>
       </c>
-      <c r="R29" s="49" t="n">
+      <c r="R29" s="50" t="n">
         <v>44.34</v>
       </c>
-      <c r="S29" s="49" t="n">
+      <c r="S29" s="50" t="n">
         <v>7.64</v>
       </c>
     </row>
@@ -6636,7 +6745,7 @@
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Tên Cột Hiển Thị</t>
+          <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
@@ -7253,7 +7362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -7327,19 +7436,19 @@
           <t>Mã Dự án</t>
         </is>
       </c>
-      <c r="C6" s="50" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>DAN-[Năm]-[STT 3 số]</t>
         </is>
       </c>
-      <c r="D6" s="50" t="inlineStr">
-        <is>
-          <t>DAN-2026-001</t>
+      <c r="D6" s="51" t="inlineStr">
+        <is>
+          <t>DAN-2026-214</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>DAN: Dự án; 2026: Năm tạo; 001: Số thứ tự tự tăng trong năm</t>
+          <t>DAN: Dự án; 2026: Năm tạo; 214: Số thứ tự tự tăng trong năm</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -7387,12 +7496,12 @@
           <t>Số / Mã Hợp đồng</t>
         </is>
       </c>
-      <c r="C8" s="50" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>HD-[Năm]-[STT 3 số]</t>
         </is>
       </c>
-      <c r="D8" s="50" t="inlineStr">
+      <c r="D8" s="51" t="inlineStr">
         <is>
           <t>HD-2026-017</t>
         </is>
@@ -7447,12 +7556,12 @@
           <t>Mã Nhà thầu / Đối tác</t>
         </is>
       </c>
-      <c r="C10" s="50" t="inlineStr">
+      <c r="C10" s="51" t="inlineStr">
         <is>
           <t>NT-[Tên viết tắt]</t>
         </is>
       </c>
-      <c r="D10" s="50" t="inlineStr">
+      <c r="D10" s="51" t="inlineStr">
         <is>
           <t>NT-CMC, NT-FPT</t>
         </is>
@@ -7507,19 +7616,19 @@
           <t>Mã Loại Dự án</t>
         </is>
       </c>
-      <c r="C12" s="50" t="inlineStr">
+      <c r="C12" s="51" t="inlineStr">
         <is>
           <t>LDA-[Tên viết tắt]</t>
         </is>
       </c>
-      <c r="D12" s="50" t="inlineStr">
-        <is>
-          <t>LDA-BT, LDA-MSPC, LDA-BQPM</t>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>LDA-NHST, LDA-HT, LDA-XDCB</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
         <is>
-          <t>LDA: Loại dự án; BT: Bảo trì, MSPC: Mua sắm phần cứng, BQPM: Bản quyền PM</t>
+          <t>LDA: Loại dự án; NHST: Ngân hàng số &amp; Thẻ, HT: Hạ tầng, XDCB: Xây dựng &amp; Bảo trì</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -7563,7 +7672,7 @@
     <row r="16">
       <c r="A16" s="28" t="inlineStr">
         <is>
-          <t>2. DANH MỤC LOẠI DỰ ÁN &amp; MÃ VIẾT TẮT</t>
+          <t>2. DANH MỤC LOẠI DỰ ÁN &amp; MÃ VIẾT TẮT (Chuẩn CSDL Production)</t>
         </is>
       </c>
     </row>
@@ -7580,7 +7689,7 @@
       </c>
       <c r="C17" s="27" t="inlineStr">
         <is>
-          <t>Tên Loại Dự Án</t>
+          <t>Tên Loại Dự Án (Hiển thị UI)</t>
         </is>
       </c>
       <c r="D17" s="27" t="inlineStr">
@@ -7593,19 +7702,19 @@
       <c r="A18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="50" t="inlineStr">
-        <is>
-          <t>LDA-BT</t>
+      <c r="B18" s="51" t="inlineStr">
+        <is>
+          <t>PL_DIGITAL_BANKING</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Bảo trì</t>
+          <t>Ngân hàng số &amp; Thẻ</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Bảo trì, bảo dưỡng hệ thống công nghệ thông tin, phần cứng và hạ tầng</t>
+          <t>Dự án liên quan đến sản phẩm, kênh số, Core banking và dịch vụ thẻ</t>
         </is>
       </c>
     </row>
@@ -7615,17 +7724,17 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>LDA-MSPC</t>
+          <t>PL_HA_TANG</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>Mua sắm phần cứng</t>
+          <t>Hạ tầng</t>
         </is>
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>Mua sắm máy chủ, thiết bị mạng, máy trạm, thiết bị lưu trữ và phụ kiện</t>
+          <t>Dự án đầu tư máy chủ, đường truyền, tủ rack, hệ thống mạng và trung tâm dữ liệu</t>
         </is>
       </c>
     </row>
@@ -7633,19 +7742,19 @@
       <c r="A20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="50" t="inlineStr">
-        <is>
-          <t>LDA-BQPM</t>
+      <c r="B20" s="51" t="inlineStr">
+        <is>
+          <t>PL_XDCB</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>Bản quyền phần mềm</t>
+          <t>Xây dựng &amp; Bảo trì</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>Mua sắm, gia hạn giấy phép bản quyền phần mềm (License / SLA)</t>
+          <t>Dự án xây dựng cơ bản, nâng cấp bảo trì hạ tầng vật lý và phòng máy</t>
         </is>
       </c>
     </row>
@@ -7655,17 +7764,17 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>LDA-TV</t>
+          <t>PL_CNTT</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>Tư vấn</t>
+          <t>Công nghệ thông tin</t>
         </is>
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>Tư vấn lập báo cáo khả thi, tư vấn thiết kế thi công, tư vấn giám sát CNTT</t>
+          <t>Dự án công nghệ thông tin tổng thể</t>
         </is>
       </c>
     </row>
@@ -7673,19 +7782,19 @@
       <c r="A22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="50" t="inlineStr">
-        <is>
-          <t>LDA-TDV</t>
+      <c r="B22" s="51" t="inlineStr">
+        <is>
+          <t>PL_HTPM</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>Thuê dịch vụ</t>
+          <t>Hệ thống phần mềm</t>
         </is>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>Thuê dịch vụ đường truyền, Cloud, dịch vụ trung tâm dữ liệu, bảo mật SOC</t>
+          <t>Dự án mua sắm, phát triển hoặc nâng cấp các hệ thống ứng dụng phần mềm</t>
         </is>
       </c>
     </row>
@@ -7695,126 +7804,166 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>LDA-KHAC</t>
+          <t>PL_SECURITY</t>
         </is>
       </c>
       <c r="C23" s="7" t="inlineStr">
         <is>
+          <t>Mạng &amp; An ninh bảo mật</t>
+        </is>
+      </c>
+      <c r="D23" s="8" t="inlineStr">
+        <is>
+          <t>Dự án trang bị tường lửa, giải pháp SIEM, SOC, kiểm thử xâm nhập ATTT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B24" s="51" t="inlineStr">
+        <is>
+          <t>PL_MSHH_DV</t>
+        </is>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>Mua sắm hàng hóa &amp; Dịch vụ</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>Mua sắm hàng hóa vật tư và thuê dịch vụ chuyên gia CNTT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>PL_KHAC</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
           <t>Khác</t>
         </is>
       </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>Các dự án đặc thù khác ngoài các danh mục trên</t>
-        </is>
-      </c>
-    </row>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Các dự án đặc thù khác</t>
+        </is>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
         <is>
           <t>3. BẢNG TRA CỨU TRẠNG THÁI THỰC HIỆN CÁC ĐỐI TƯỢNG</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B29" s="25" t="inlineStr">
         <is>
           <t>Đối Tượng</t>
         </is>
       </c>
-      <c r="C27" s="25" t="inlineStr">
+      <c r="C29" s="25" t="inlineStr">
         <is>
           <t>Giá Trị Trạng Thái Trong DB (Enum / Id)</t>
         </is>
       </c>
-      <c r="D27" s="25" t="inlineStr">
-        <is>
-          <t>Tên Hiển Thị Chuẩn Trên Báo Cáo</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B28" s="11" t="inlineStr">
-        <is>
-          <t>Dự án (DuAn)</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>1: Chưa triển khai | 2: Đang triển khai | 3: Tạm dừng | 4: Hoàn thành | 5: Đã hủy</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>Chưa triển khai | Đang triển khai | Tạm dừng | Đã nghiệm thu/hoàn thành | Đã hủy</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Gói thầu (GoiThau)</t>
-        </is>
-      </c>
-      <c r="C29" s="8" t="inlineStr">
-        <is>
-          <t>1: Chưa LCNT | 2: Đang LCNT | 3: Đã phê duyệt KQLCNT | 4: Đã ký HĐ | 5: Hoàn thành | 6: Đã hủy</t>
-        </is>
-      </c>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>Chưa LCNT | Đang tổ chức LCNT | Đã phê duyệt KQLCNT | Đã hoàn thành LCNT | Đã hủy</t>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>Tên Hiển Thị Chuẩn Trên Báo Cáo &amp; UI</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Hợp đồng (HopDong)</t>
+          <t>Dự án (DuAn)</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>IsActive = true/false, ExpiredDate so với Today, DaKetThuc</t>
+          <t>1: Chuẩn bị đầu tư (Draft/Submitted) | 4: Đang triển khai | 5: Nghiệm thu | 6: Thanh toán | 7: Quyết toán | 8: Hoàn thành | 9: Tạm dừng | 10: Đã gộp</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Đang thực hiện | Sắp hết hạn | Đã hết hạn | Đã thanh lý/hoàn thành</t>
+          <t>Chuẩn bị đầu tư | Đang triển khai | Nghiệm thu | Thanh toán | Quyết toán | Hoàn thành | Tạm dừng | Đã gộp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Gói thầu (GoiThau)</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>1: Chưa LCNT | 2: Đang LCNT | 3: Đã phê duyệt KQLCNT | 4: Đã ký HĐ | 5: Hoàn thành | 6: Đã hủy</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Chưa LCNT | Đang tổ chức LCNT | Đã phê duyệt KQLCNT | Đã hoàn thành LCNT | Đã hủy</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Hợp đồng (HopDong)</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>IsActive = true/false, ExpiredDate so với Today, DaKetThuc</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Đang thực hiện | Sắp hết hạn | Đã hết hạn | Đã thanh lý/hoàn thành</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>Đợt thanh toán (DotThanhToan)</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>IsPaid = false (Chưa thanh toán) | IsPaid = true (Đã thanh toán)</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D33" s="8" t="inlineStr">
         <is>
           <t>🟡 Chưa thanh toán | 🟢 Đã thanh toán</t>
         </is>
@@ -7823,7 +7972,7 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:D28"/>
     <mergeCell ref="A4:F4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/Mau_Bao_Cao_Va_Data_Mapping_QLDA.xlsx
+++ b/docs/Mau_Bao_Cao_Va_Data_Mapping_QLDA.xlsx
@@ -94,6 +94,12 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="001E293B"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00047857"/>
       <sz val="9"/>
     </font>
@@ -133,14 +139,8 @@
       <color rgb="001E3A8A"/>
       <sz val="9"/>
     </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001E293B"/>
-      <sz val="8"/>
-    </font>
   </fonts>
-  <fills count="18">
+  <fills count="20">
     <fill>
       <patternFill/>
     </fill>
@@ -243,6 +243,18 @@
         <bgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E7FF"/>
+        <bgColor rgb="00E0E7FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -270,7 +282,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -332,7 +344,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -359,30 +380,39 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -773,7 +803,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TỔNG HỢP BIỂU MẪU BÁO CÁO THỰC TẾ &amp; MÔ TẢ DATA MAPPING NGUỒN CSDL (CẬP NHẬT THEO HỆ THỐNG ĐANG CHẠY)</t>
+          <t>TỔNG HỢP BIỂU MẪU BÁO CÁO THỰC TẾ &amp; MÔ TẢ DATA MAPPING NGUỒN CSDL</t>
         </is>
       </c>
     </row>
@@ -865,7 +895,7 @@
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>Quản lý liên kết gộp dự án nguồn và triển khai, phân kỳ vốn động theo khoảng năm tra cứu, vốn chưa phân bổ</t>
+          <t>Quản lý liên kết gộp dự án nguồn và triển khai, phân nhóm nguồn vốn theo từng năm tra cứu (Tiêu đề chính: Năm; Cấp con: Các nguồn vốn)</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
@@ -880,7 +910,7 @@
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Đã hiển thị cột phân kỳ động, bỏ chữ VNĐ</t>
+          <t>Đã phân cấp nguồn vốn dưới từng năm, bỏ chữ VNĐ</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -1959,28 +1989,6 @@
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="14" t="inlineStr">
-        <is>
-          <t>📌 GHI CHÚ ĐIỀU CHỈNH:</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="inlineStr">
-        <is>
-          <t>- Đã bổ sung cột [TÊN DỰ ÁN TRIỂN KHAI] ngay sau cột [MÃ DỰ ÁN].</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="inlineStr">
-        <is>
-          <t>- Đã xóa bỏ cột [Cảnh báo rủi ro (RAG)] để đúng 100% với thực trạng giao diện phần mềm đang có.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A21:K21"/>
@@ -1998,21 +2006,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:R42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="48" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="48" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="23" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="33" customWidth="1" min="11" max="11"/>
-    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="8" max="8"/>
+    <col width="24" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="13" max="13"/>
+    <col width="27" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="33" customWidth="1" min="17" max="17"/>
+    <col width="19" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2025,7 +2039,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Theo dõi quan hệ phân bổ vốn từ dự án nguồn sang dự án triển khai, phân kỳ vốn theo các năm và vốn còn lại</t>
+          <t>Quản lý phân bổ vốn theo năm được chọn, trong đó từng Năm là Tiêu đề chính và dưới đó là chi tiết các Nguồn vốn</t>
         </is>
       </c>
     </row>
@@ -2067,17 +2081,17 @@
       </c>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t>Dải năm tra cứu (Ví dụ: 2025 - 2027)</t>
+          <t>Dải năm tra cứu (Ví dụ: 2025 - 2026 hoặc 2025 - 2027)</t>
         </is>
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>Hệ thống tự động sinh các cột Phân kỳ vốn tương ứng theo từng năm trong khoảng tra cứu</t>
+          <t>Hệ thống tự động sinh cụm cột Kế hoạch vốn cho từng năm. Mỗi năm gồm Tiêu đề chính (Năm) và các cột nguồn vốn con bên dưới</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Các cột phân kỳ sinh động</t>
+          <t>Phân cấp tiêu đề động theo năm</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2198,7 @@
       </c>
       <c r="F13" s="27" t="inlineStr">
         <is>
-          <t>Mã DA triển khai</t>
+          <t>Mã DA triển khai liên kết</t>
         </is>
       </c>
       <c r="G13" s="27" t="inlineStr">
@@ -2194,418 +2208,612 @@
       </c>
       <c r="H13" s="27" t="inlineStr">
         <is>
-          <t>Vốn phân bổ DA triển khai</t>
+          <t>Vốn phân bổ cho DA triển khai</t>
         </is>
       </c>
       <c r="I13" s="27" t="inlineStr">
         <is>
-          <t>Phân kỳ vốn năm 2025</t>
-        </is>
-      </c>
-      <c r="J13" s="27" t="inlineStr">
-        <is>
-          <t>Phân kỳ vốn năm 2026</t>
-        </is>
-      </c>
-      <c r="K13" s="27" t="inlineStr">
+          <t>KẾ HOẠCH VỐN NĂM 2025</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n"/>
+      <c r="K13" s="23" t="n"/>
+      <c r="L13" s="23" t="n"/>
+      <c r="M13" s="27" t="inlineStr">
+        <is>
+          <t>KẾ HOẠCH VỐN NĂM 2026</t>
+        </is>
+      </c>
+      <c r="N13" s="23" t="n"/>
+      <c r="O13" s="23" t="n"/>
+      <c r="P13" s="23" t="n"/>
+      <c r="Q13" s="27" t="inlineStr">
         <is>
           <t>Vốn nguồn còn lại chưa phân bổ</t>
         </is>
       </c>
-      <c r="L13" s="27" t="inlineStr">
+      <c r="R13" s="27" t="inlineStr">
         <is>
           <t>Trạng thái nguồn</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>PRJ-030</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>Nâng cấp hệ thống E-Bank</t>
-        </is>
-      </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>QĐ-2026/01</t>
-        </is>
-      </c>
-      <c r="E14" s="29" t="inlineStr">
-        <is>
-          <t>2.271.000.000</t>
-        </is>
-      </c>
-      <c r="F14" s="20" t="inlineStr">
-        <is>
-          <t>DAN-2026-155</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Phát triển module QLDA E-Bank</t>
-        </is>
-      </c>
-      <c r="H14" s="29" t="inlineStr">
-        <is>
-          <t>2.271.000.000</t>
-        </is>
-      </c>
+      <c r="A14" s="23" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="23" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="23" t="n"/>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Tổng năm 2025</t>
         </is>
       </c>
       <c r="J14" s="29" t="inlineStr">
         <is>
-          <t>123.333.000</t>
+          <t>Vốn điều lệ &amp; Quỹ dự trữ</t>
         </is>
       </c>
       <c r="K14" s="29" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" s="9" t="inlineStr">
-        <is>
-          <t>Đã phân bổ hết</t>
-        </is>
-      </c>
+          <t>Quỹ ĐTPT</t>
+        </is>
+      </c>
+      <c r="L14" s="29" t="inlineStr">
+        <is>
+          <t>Nguồn khác</t>
+        </is>
+      </c>
+      <c r="M14" s="29" t="inlineStr">
+        <is>
+          <t>Tổng năm 2026</t>
+        </is>
+      </c>
+      <c r="N14" s="29" t="inlineStr">
+        <is>
+          <t>Vốn điều lệ &amp; Quỹ dự trữ</t>
+        </is>
+      </c>
+      <c r="O14" s="29" t="inlineStr">
+        <is>
+          <t>Quỹ ĐTPT</t>
+        </is>
+      </c>
+      <c r="P14" s="29" t="inlineStr">
+        <is>
+          <t>Nguồn khác</t>
+        </is>
+      </c>
+      <c r="Q14" s="23" t="n"/>
+      <c r="R14" s="23" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>PRJ-035</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Hiện đại hóa hạ tầng mạng TTCNTT</t>
-        </is>
-      </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>QĐ-2026/45</t>
-        </is>
-      </c>
-      <c r="E15" s="29" t="inlineStr">
-        <is>
-          <t>5.000.000.000</t>
-        </is>
-      </c>
-      <c r="F15" s="20" t="inlineStr">
-        <is>
-          <t>DAN-2026-160</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>Thay thế switch core tòa nhà 15T</t>
-        </is>
-      </c>
-      <c r="H15" s="29" t="inlineStr">
-        <is>
-          <t>3.200.000.000</t>
-        </is>
-      </c>
-      <c r="I15" s="29" t="inlineStr">
-        <is>
-          <t>1.500.000.000</t>
-        </is>
-      </c>
-      <c r="J15" s="29" t="inlineStr">
-        <is>
-          <t>1.700.000.000</t>
-        </is>
-      </c>
-      <c r="K15" s="29" t="inlineStr">
-        <is>
-          <t>1.800.000.000</t>
-        </is>
-      </c>
-      <c r="L15" s="9" t="inlineStr">
-        <is>
-          <t>Đang phân bổ</t>
+      <c r="A15" s="30" t="inlineStr">
+        <is>
+          <t>(1)</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>(2)</t>
+        </is>
+      </c>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>(3)</t>
+        </is>
+      </c>
+      <c r="D15" s="30" t="inlineStr">
+        <is>
+          <t>(4)</t>
+        </is>
+      </c>
+      <c r="E15" s="30" t="inlineStr">
+        <is>
+          <t>(5)</t>
+        </is>
+      </c>
+      <c r="F15" s="30" t="inlineStr">
+        <is>
+          <t>(6)</t>
+        </is>
+      </c>
+      <c r="G15" s="30" t="inlineStr">
+        <is>
+          <t>(7)</t>
+        </is>
+      </c>
+      <c r="H15" s="30" t="inlineStr">
+        <is>
+          <t>(8)</t>
+        </is>
+      </c>
+      <c r="I15" s="30" t="inlineStr">
+        <is>
+          <t>(9)</t>
+        </is>
+      </c>
+      <c r="J15" s="30" t="inlineStr">
+        <is>
+          <t>(10)</t>
+        </is>
+      </c>
+      <c r="K15" s="30" t="inlineStr">
+        <is>
+          <t>(11)</t>
+        </is>
+      </c>
+      <c r="L15" s="30" t="inlineStr">
+        <is>
+          <t>(12)</t>
+        </is>
+      </c>
+      <c r="M15" s="30" t="inlineStr">
+        <is>
+          <t>(13)</t>
+        </is>
+      </c>
+      <c r="N15" s="30" t="inlineStr">
+        <is>
+          <t>(14)</t>
+        </is>
+      </c>
+      <c r="O15" s="30" t="inlineStr">
+        <is>
+          <t>(15)</t>
+        </is>
+      </c>
+      <c r="P15" s="30" t="inlineStr">
+        <is>
+          <t>(16)</t>
+        </is>
+      </c>
+      <c r="Q15" s="30" t="inlineStr">
+        <is>
+          <t>(17)</t>
+        </is>
+      </c>
+      <c r="R15" s="30" t="inlineStr">
+        <is>
+          <t>(18)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>PRJ-030</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>Nâng cấp hệ thống E-Bank</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>QĐ-2026/01</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>2.271.000.000</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>DAN-2026-155</t>
+        </is>
+      </c>
+      <c r="G16" s="8" t="inlineStr">
+        <is>
+          <t>Phát triển module QLDA E-Bank</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>2.271.000.000</t>
+        </is>
+      </c>
+      <c r="I16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M16" s="31" t="inlineStr">
+        <is>
+          <t>123.333.000</t>
+        </is>
+      </c>
+      <c r="N16" s="31" t="inlineStr">
+        <is>
+          <t>123.333.000</t>
+        </is>
+      </c>
+      <c r="O16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q16" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R16" s="9" t="inlineStr">
+        <is>
+          <t>Đã phân bổ</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>PRJ-035</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Hiện đại hóa hạ tầng mạng TTCNTT</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>QĐ-2026/45</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>5.000.000.000</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>DAN-2026-160</t>
+        </is>
+      </c>
+      <c r="G17" s="8" t="inlineStr">
+        <is>
+          <t>Thay thế switch core tòa 15T</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>3.200.000.000</t>
+        </is>
+      </c>
+      <c r="I17" s="31" t="inlineStr">
+        <is>
+          <t>1.500.000.000</t>
+        </is>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>1.000.000.000</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>500.000.000</t>
+        </is>
+      </c>
+      <c r="L17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M17" s="31" t="inlineStr">
+        <is>
+          <t>1.700.000.000</t>
+        </is>
+      </c>
+      <c r="N17" s="31" t="inlineStr">
+        <is>
+          <t>1.200.000.000</t>
+        </is>
+      </c>
+      <c r="O17" s="31" t="inlineStr">
+        <is>
+          <t>500.000.000</t>
+        </is>
+      </c>
+      <c r="P17" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q17" s="31" t="inlineStr">
+        <is>
+          <t>1.800.000.000</t>
+        </is>
+      </c>
+      <c r="R17" s="9" t="inlineStr">
+        <is>
+          <t>Đang phân bổ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>PRJ-040</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C18" s="8" t="inlineStr">
         <is>
           <t>Xây dựng hệ thống Data Warehouse</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t>QĐ-2026/89</t>
         </is>
       </c>
-      <c r="E16" s="29" t="inlineStr">
+      <c r="E18" s="31" t="inlineStr">
         <is>
           <t>12.500.000.000</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F18" s="20" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="G18" s="8" t="inlineStr">
         <is>
           <t>(Chưa tạo DA liên kết)</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I18" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr">
+      <c r="J18" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="29" t="inlineStr">
+      <c r="K18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" s="31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q18" s="31" t="inlineStr">
         <is>
           <t>12.500.000.000</t>
         </is>
       </c>
-      <c r="L16" s="9" t="inlineStr">
+      <c r="R18" s="9" t="inlineStr">
         <is>
           <t>Chưa phân bổ</t>
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18"/>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
-        <is>
-          <t>3. MÔ TẢ CHI TIẾT NGUỒN DỮ LIỆU &amp; LOGIC TÍNH TOÁN (DATA MAPPING)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="inlineStr">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="32" t="inlineStr">
+        <is>
+          <t>19.771.000.000</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="23" t="n"/>
+      <c r="H19" s="32" t="inlineStr">
+        <is>
+          <t>5.471.000.000</t>
+        </is>
+      </c>
+      <c r="I19" s="32" t="inlineStr">
+        <is>
+          <t>1.500.000.000</t>
+        </is>
+      </c>
+      <c r="J19" s="23" t="n"/>
+      <c r="K19" s="23" t="n"/>
+      <c r="L19" s="23" t="n"/>
+      <c r="M19" s="32" t="inlineStr">
+        <is>
+          <t>1.823.333.000</t>
+        </is>
+      </c>
+      <c r="N19" s="23" t="n"/>
+      <c r="O19" s="23" t="n"/>
+      <c r="P19" s="23" t="n"/>
+      <c r="Q19" s="32" t="inlineStr">
+        <is>
+          <t>14.300.000.000</t>
+        </is>
+      </c>
+      <c r="R19" s="23" t="n"/>
+    </row>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="24" t="inlineStr">
+        <is>
+          <t>3. MÔ TẢ CHI TIẾT NGUỒN DỮ LIỆU &amp; LOGIC TÍNH TOÁN (DATA MAPPING - Cụm nguồn vốn theo năm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B23" s="25" t="inlineStr">
         <is>
           <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
-      <c r="C20" s="25" t="inlineStr">
+      <c r="C23" s="25" t="inlineStr">
         <is>
           <t>Bảng / Entity Nguồn</t>
         </is>
       </c>
-      <c r="D20" s="25" t="inlineStr">
+      <c r="D23" s="25" t="inlineStr">
         <is>
           <t>Trường Dữ Liệu (Field)</t>
         </is>
       </c>
-      <c r="E20" s="25" t="inlineStr">
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>Kiểu Dữ Liệu</t>
         </is>
       </c>
-      <c r="F20" s="25" t="inlineStr">
+      <c r="F23" s="25" t="inlineStr">
         <is>
           <t>Logic Lấy Dữ Liệu &amp; Công Thức Tính Toán Chi Tiết</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>STT</t>
-        </is>
-      </c>
-      <c r="C21" s="8" t="inlineStr">
-        <is>
-          <t>Chương trình (System)</t>
-        </is>
-      </c>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>Index tự tăng</t>
-        </is>
-      </c>
-      <c r="E21" s="9" t="inlineStr">
-        <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>Số thứ tự của dòng dữ liệu</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Mã dự án nguồn</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (hoặc DuAnGopLinks.SourceDuAn)</t>
-        </is>
-      </c>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>SourceDuAn.Code</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F22" s="12" t="inlineStr">
-        <is>
-          <t>Mã của dự án nguồn cung cấp nguồn vốn (Code của DuAn đóng vai trò nguồn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Tên dự án nguồn</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (hoặc DuAnGopLinks.SourceDuAn)</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>SourceDuAn.Name</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>Tên đầy đủ của dự án nguồn</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Số QĐ phê duyệt</t>
+          <t>(1) STT</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAns (Dự án nguồn)</t>
+          <t>Chương trình (System)</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>SourceDuAn.SoQuyetDinh</t>
+          <t>Index tự tăng</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
         <is>
-          <t>Số quyết định phê duyệt chủ trương / dự toán của dự án nguồn</t>
+          <t>Số thứ tự dòng trong báo cáo</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Tổng vốn phê duyệt</t>
+          <t>(2) Mã dự án nguồn</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAns / DuAnNguonVons</t>
+          <t>Bảng DuAns (Dự án nguồn)</t>
         </is>
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>SourceDuAn.DuToanPheDuyet</t>
+          <t>SourceDuAn.Code</t>
         </is>
       </c>
       <c r="E25" s="9" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>Tổng mức vốn đầu tư được phê duyệt của dự án nguồn (hoặc Sum(DuAnNguonVon.GiaTri))</t>
+          <t>Mã của dự án nguồn cấp vốn (DuAn.Code của DA vai trò nguồn)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Mã DA triển khai liên kết</t>
+          <t>(3) Tên dự án nguồn</t>
         </is>
       </c>
       <c r="C26" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAnGopLinks &amp; DuAns</t>
+          <t>Bảng DuAns (Dự án nguồn)</t>
         </is>
       </c>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>TargetDuAn.Code</t>
+          <t>SourceDuAn.Name</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -2615,27 +2823,27 @@
       </c>
       <c r="F26" s="12" t="inlineStr">
         <is>
-          <t>Mã của dự án triển khai được liên kết nhận vốn phân bổ từ dự án nguồn</t>
+          <t>Tên đầy đủ của dự án nguồn</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Tên dự án triển khai</t>
+          <t>(4) Số QĐ phê duyệt</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAnGopLinks &amp; DuAns</t>
+          <t>Bảng DuAns (Dự án nguồn)</t>
         </is>
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>TargetDuAn.Name</t>
+          <t>SourceDuAn.SoQuyetDinh</t>
         </is>
       </c>
       <c r="E27" s="9" t="inlineStr">
@@ -2645,27 +2853,27 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>Tên đầy đủ của dự án triển khai</t>
+          <t>Số quyết định phê duyệt chủ trương / dự toán của dự án nguồn</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Vốn phân bổ DA triển khai</t>
+          <t>(5) Tổng vốn phê duyệt</t>
         </is>
       </c>
       <c r="C28" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAnGopLinks / DuAns</t>
+          <t>Bảng DuAns / DuAnNguonVons</t>
         </is>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
-          <t>DuAnGopLink.GiaTriPhanBo hoặc TargetDuAn.DuToanPheDuyet</t>
+          <t>SourceDuAn.DuToanPheDuyet</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -2675,108 +2883,350 @@
       </c>
       <c r="F28" s="12" t="inlineStr">
         <is>
-          <t>Số tiền vốn được trích phân bổ cho dự án triển khai cụ thể này</t>
+          <t>Tổng mức vốn đầu tư được phê duyệt của dự án nguồn</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Phân kỳ vốn năm [Năm]</t>
+          <t>(6) Mã DA triển khai liên kết</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAnPhanKyVons</t>
+          <t>Bảng DuAnGopLinks &amp; DuAns</t>
         </is>
       </c>
       <c r="D29" s="8" t="inlineStr">
         <is>
-          <t>DuAnPhanKyVon.GiaTri</t>
+          <t>TargetDuAn.Code</t>
         </is>
       </c>
       <c r="E29" s="9" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>Giá trị phân kỳ vốn theo từng năm của dự án triển khai: PhanKyVons.Where(p =&gt; p.Nam == year).Sum(p =&gt; p.GiaTri). Các cột này sinh động theo dải năm tra cứu</t>
+          <t>Mã của dự án triển khai được liên kết nhận vốn phân bổ từ dự án nguồn</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Vốn nguồn còn lại chưa phân bổ</t>
+          <t>(7) Tên dự án triển khai</t>
         </is>
       </c>
       <c r="C30" s="12" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng DuAnGopLinks &amp; DuAns</t>
         </is>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
-          <t>Tổng vốn nguồn - Sum(Vốn đã phân bổ)</t>
+          <t>TargetDuAn.Name</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
         <is>
-          <t>Bằng Tổng vốn phê duyệt của DA nguồn trừ đi tổng số vốn đã phân bổ cho tất cả các DA triển khai liên kết</t>
+          <t>Tên đầy đủ của dự án triển khai liên kết</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>(8) Vốn phân bổ DA triển khai</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>Bảng DuAnGopLinks / DuAns</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>DuAnGopLink.GiaTriPhanBo hoặc TargetDuAn.DuToanPheDuyet</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Số tiền vốn được trích phân bổ cho dự án triển khai cụ thể này</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>(9) Tổng vốn năm [Y]</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DuAnNguonVons</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>Sum(DuAnNguonVon.SoTien Where Nam == Y)</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F32" s="12" t="inlineStr">
+        <is>
+          <t>Tổng kế hoạch vốn dự án trong năm Y: TargetDuAn.DanhSachNguonVon.Where(nv =&gt; nv.Nam == Y).Sum(nv =&gt; nv.SoTien)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>(10) Vốn điều lệ &amp; Quỹ dự trữ [Y]</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Bảng DuAnNguonVons (DanhMuc NguonVon)</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>DuAnNguonVon (Code == 'NV_VDL_QDTR' &amp; Nam == Y)</t>
+        </is>
+      </c>
+      <c r="E33" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Số vốn phân kỳ từ nguồn Vốn điều lệ và Quỹ dự trữ bổ sung vốn điều lệ trong năm Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Trạng thái nguồn</t>
-        </is>
-      </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>(11) Quỹ đầu tư phát triển [Y]</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DuAnNguonVons (DanhMuc NguonVon)</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>DuAnNguonVon (Code == 'NV_QDTPT' &amp; Nam == Y)</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F34" s="12" t="inlineStr">
+        <is>
+          <t>Số vốn phân kỳ từ Quỹ đầu tư phát triển trong năm Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>(12) Nguồn khác [Y]</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="inlineStr">
+        <is>
+          <t>Bảng DuAnNguonVons</t>
+        </is>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>DuAnNguonVon (Các nguồn còn lại &amp; Nam == Y)</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Số vốn phân kỳ từ các nguồn vốn hợp pháp khác trong năm Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>(13)-(16) Cụm nguồn vốn năm tiếp theo</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DuAnNguonVons</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Tương tự cụm cột (9)-(12) cho năm tiếp theo</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Cấu trúc lặp lại động theo từng năm được chọn trong khoảng tra cứu (ví dụ Năm 2026, 2027...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>(17) Vốn nguồn còn lại chưa phân bổ</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="inlineStr">
         <is>
           <t>Tính toán động</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Tổng vốn nguồn - Sum(Vốn đã phân bổ)</t>
+        </is>
+      </c>
+      <c r="E37" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Bằng Tổng vốn phê duyệt của DA nguồn trừ đi tổng số vốn đã phân bổ cho các DA triển khai liên kết</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>(18) Trạng thái nguồn</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>Tính toán động</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
         <is>
           <t>Calculated Status</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr">
+      <c r="E38" s="13" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
-        <is>
-          <t>Đánh giá trạng thái nguồn: 
-- 'Đã phân bổ hết' (nếu Vốn còn lại &lt;= 0)
-- 'Đang phân bổ' (nếu 0 &lt; Vốn còn lại &lt; Tổng vốn)
-- 'Chưa phân bổ' (nếu chưa gán cho DA triển khai nào)</t>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Đánh giá trạng thái nguồn: 'Đã phân bổ' (hết), 'Đang phân bổ' (còn dư), 'Chưa phân bổ'</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="14" t="inlineStr">
+        <is>
+          <t>📌 GHI CHÚ ĐIỀU CHỈNH:</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="inlineStr">
+        <is>
+          <t>- Tiêu đề nhóm Cấp 1 là các NĂM tra cứu (ví dụ: KẾ HOẠCH VỐN NĂM 2025, KẾ HOẠCH VỐN NĂM 2026...).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="15" t="inlineStr">
+        <is>
+          <t>- Dưới mỗi Năm (Cấp 2) phân rã thành các cột: Tổng năm, Vốn điều lệ &amp; Quỹ dự trữ, Quỹ ĐTPT, Nguồn khác theo đúng thực tế CSDL DuAnNguonVon.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A19:F19"/>
+  <mergeCells count="16">
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="I13:L13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="R13:R14"/>
+    <mergeCell ref="A13:A14"/>
     <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A12:L12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="Q13:Q14"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A12:R12"/>
+    <mergeCell ref="C13:C14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2823,29 +3273,29 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="30" t="inlineStr">
+      <c r="A4" s="33" t="inlineStr">
         <is>
           <t>1. BỘ LỌC &amp; TÌM KIẾM (FILTERS &amp; SEARCH)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>Tiêu chí lọc / Tìm kiếm</t>
         </is>
       </c>
-      <c r="B5" s="31" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>Các lựa chọn / Phạm vi</t>
         </is>
       </c>
-      <c r="C5" s="31" t="inlineStr">
+      <c r="C5" s="34" t="inlineStr">
         <is>
           <t>Quy tắc nghiệp vụ &amp; Điều chỉnh</t>
         </is>
       </c>
-      <c r="D5" s="31" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
@@ -2942,79 +3392,79 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="35" t="inlineStr">
         <is>
           <t>2. BIỂU MẪU DỮ LIỆU CHI TIẾT (REPORT DATA PREVIEW) - Đơn vị tính: Đồng</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="inlineStr">
+      <c r="A13" s="34" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B13" s="31" t="inlineStr">
+      <c r="B13" s="34" t="inlineStr">
         <is>
           <t>Mã dự án</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
+      <c r="C13" s="34" t="inlineStr">
         <is>
           <t>Mã gói thầu</t>
         </is>
       </c>
-      <c r="D13" s="31" t="inlineStr">
+      <c r="D13" s="34" t="inlineStr">
         <is>
           <t>Tên gói thầu</t>
         </is>
       </c>
-      <c r="E13" s="31" t="inlineStr">
+      <c r="E13" s="34" t="inlineStr">
         <is>
           <t>Số QĐ phê duyệt KHLCNT</t>
         </is>
       </c>
-      <c r="F13" s="31" t="inlineStr">
+      <c r="F13" s="34" t="inlineStr">
         <is>
           <t>Số QĐ phê duyệt KQLCNT</t>
         </is>
       </c>
-      <c r="G13" s="31" t="inlineStr">
+      <c r="G13" s="34" t="inlineStr">
         <is>
           <t>Giá trị dự toán</t>
         </is>
       </c>
-      <c r="H13" s="31" t="inlineStr">
+      <c r="H13" s="34" t="inlineStr">
         <is>
           <t>Hình thức LCNT</t>
         </is>
       </c>
-      <c r="I13" s="31" t="inlineStr">
+      <c r="I13" s="34" t="inlineStr">
         <is>
           <t>Phương thức LCNT</t>
         </is>
       </c>
-      <c r="J13" s="31" t="inlineStr">
+      <c r="J13" s="34" t="inlineStr">
         <is>
           <t>Tổng giá trị HĐ đã ký</t>
         </is>
       </c>
-      <c r="K13" s="31" t="inlineStr">
+      <c r="K13" s="34" t="inlineStr">
         <is>
           <t>Giá trị tiết kiệm</t>
         </is>
       </c>
-      <c r="L13" s="31" t="inlineStr">
+      <c r="L13" s="34" t="inlineStr">
         <is>
           <t>Tỷ lệ sử dụng dự toán (%)</t>
         </is>
       </c>
-      <c r="M13" s="31" t="inlineStr">
+      <c r="M13" s="34" t="inlineStr">
         <is>
           <t>Tên nhà thầu</t>
         </is>
       </c>
-      <c r="N13" s="31" t="inlineStr">
+      <c r="N13" s="34" t="inlineStr">
         <is>
           <t>Trạng thái gói thầu</t>
         </is>
@@ -3049,7 +3499,7 @@
           <t>342/QĐ-NHHT</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="31" t="inlineStr">
         <is>
           <t>500.000.000</t>
         </is>
@@ -3064,12 +3514,12 @@
           <t>1 GĐ 1 THS</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J14" s="31" t="inlineStr">
         <is>
           <t>485.000.000</t>
         </is>
       </c>
-      <c r="K14" s="29" t="inlineStr">
+      <c r="K14" s="31" t="inlineStr">
         <is>
           <t>15.000.000</t>
         </is>
@@ -3119,7 +3569,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr">
+      <c r="G15" s="31" t="inlineStr">
         <is>
           <t>1.200.000.000</t>
         </is>
@@ -3134,12 +3584,12 @@
           <t>1 GĐ 1 THS</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K15" s="29" t="inlineStr">
+      <c r="K15" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -3189,7 +3639,7 @@
           <t>288/QĐ-NHHT</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>350.000.000</t>
         </is>
@@ -3204,12 +3654,12 @@
           <t>1 GĐ 1 THS</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr">
+      <c r="J16" s="31" t="inlineStr">
         <is>
           <t>340.000.000</t>
         </is>
       </c>
-      <c r="K16" s="29" t="inlineStr">
+      <c r="K16" s="31" t="inlineStr">
         <is>
           <t>10.000.000</t>
         </is>
@@ -3741,29 +4191,29 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="33" t="inlineStr">
+      <c r="A4" s="36" t="inlineStr">
         <is>
           <t>1. BỘ LỌC &amp; TÌM KIẾM (FILTERS &amp; SEARCH)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="34" t="inlineStr">
+      <c r="A5" s="37" t="inlineStr">
         <is>
           <t>Tiêu chí lọc / Tìm kiếm</t>
         </is>
       </c>
-      <c r="B5" s="34" t="inlineStr">
+      <c r="B5" s="37" t="inlineStr">
         <is>
           <t>Các lựa chọn / Phạm vi</t>
         </is>
       </c>
-      <c r="C5" s="34" t="inlineStr">
+      <c r="C5" s="37" t="inlineStr">
         <is>
           <t>Quy tắc nghiệp vụ &amp; Điều chỉnh</t>
         </is>
       </c>
-      <c r="D5" s="34" t="inlineStr">
+      <c r="D5" s="37" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
@@ -3860,74 +4310,74 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="38" t="inlineStr">
         <is>
           <t>2. BIỂU MẪU DỮ LIỆU CHI TIẾT (REPORT DATA PREVIEW) - Đơn vị tính: Đồng</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="37" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="37" t="inlineStr">
         <is>
           <t>Số / Mã HĐ</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="37" t="inlineStr">
         <is>
           <t>Tên Hợp đồng kinh tế</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="37" t="inlineStr">
         <is>
           <t>Dự án triển khai liên kết</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="37" t="inlineStr">
         <is>
           <t>Nhà thầu</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Người đại diện</t>
         </is>
       </c>
-      <c r="G13" s="34" t="inlineStr">
+      <c r="G13" s="37" t="inlineStr">
         <is>
           <t>Giá trị HĐ</t>
         </is>
       </c>
-      <c r="H13" s="34" t="inlineStr">
+      <c r="H13" s="37" t="inlineStr">
         <is>
           <t>Giá trị đã thanh toán lũy kế</t>
         </is>
       </c>
-      <c r="I13" s="34" t="inlineStr">
+      <c r="I13" s="37" t="inlineStr">
         <is>
           <t>Giá trị còn lại chưa thanh toán</t>
         </is>
       </c>
-      <c r="J13" s="34" t="inlineStr">
+      <c r="J13" s="37" t="inlineStr">
         <is>
           <t>Ngày ký</t>
         </is>
       </c>
-      <c r="K13" s="34" t="inlineStr">
+      <c r="K13" s="37" t="inlineStr">
         <is>
           <t>Ngày hết hạn</t>
         </is>
       </c>
-      <c r="L13" s="34" t="inlineStr">
+      <c r="L13" s="37" t="inlineStr">
         <is>
           <t>Số ngày còn lại</t>
         </is>
       </c>
-      <c r="M13" s="34" t="inlineStr">
+      <c r="M13" s="37" t="inlineStr">
         <is>
           <t>Trạng thái thực hiện</t>
         </is>
@@ -3962,17 +4412,17 @@
           <t>Lê Văn T</t>
         </is>
       </c>
-      <c r="G14" s="29" t="inlineStr">
+      <c r="G14" s="31" t="inlineStr">
         <is>
           <t>500.000.000</t>
         </is>
       </c>
-      <c r="H14" s="29" t="inlineStr">
+      <c r="H14" s="31" t="inlineStr">
         <is>
           <t>200.000.000</t>
         </is>
       </c>
-      <c r="I14" s="29" t="inlineStr">
+      <c r="I14" s="31" t="inlineStr">
         <is>
           <t>300.000.000</t>
         </is>
@@ -4025,17 +4475,17 @@
           <t>Trần Đình K</t>
         </is>
       </c>
-      <c r="G15" s="29" t="inlineStr">
+      <c r="G15" s="31" t="inlineStr">
         <is>
           <t>1.200.000.000</t>
         </is>
       </c>
-      <c r="H15" s="29" t="inlineStr">
+      <c r="H15" s="31" t="inlineStr">
         <is>
           <t>600.000.000</t>
         </is>
       </c>
-      <c r="I15" s="29" t="inlineStr">
+      <c r="I15" s="31" t="inlineStr">
         <is>
           <t>600.000.000</t>
         </is>
@@ -4088,17 +4538,17 @@
           <t>Nguyễn Văn H</t>
         </is>
       </c>
-      <c r="G16" s="29" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>450.000.000</t>
         </is>
       </c>
-      <c r="H16" s="29" t="inlineStr">
+      <c r="H16" s="31" t="inlineStr">
         <is>
           <t>450.000.000</t>
         </is>
       </c>
-      <c r="I16" s="29" t="inlineStr">
+      <c r="I16" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -4604,29 +5054,29 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="36" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>1. BỘ LỌC &amp; TÌM KIẾM (FILTERS &amp; SEARCH)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="37" t="inlineStr">
+      <c r="A5" s="40" t="inlineStr">
         <is>
           <t>Tiêu chí lọc / Tìm kiếm</t>
         </is>
       </c>
-      <c r="B5" s="37" t="inlineStr">
+      <c r="B5" s="40" t="inlineStr">
         <is>
           <t>Các lựa chọn / Phạm vi</t>
         </is>
       </c>
-      <c r="C5" s="37" t="inlineStr">
+      <c r="C5" s="40" t="inlineStr">
         <is>
           <t>Quy tắc nghiệp vụ &amp; Điều chỉnh</t>
         </is>
       </c>
-      <c r="D5" s="37" t="inlineStr">
+      <c r="D5" s="40" t="inlineStr">
         <is>
           <t>Ghi chú</t>
         </is>
@@ -4723,59 +5173,59 @@
     <row r="10"/>
     <row r="11"/>
     <row r="12">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="A12" s="41" t="inlineStr">
         <is>
           <t>2. BIỂU MẪU DỮ LIỆU CHI TIẾT (REPORT DATA PREVIEW) - Đơn vị tính: Đồng</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="40" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="40" t="inlineStr">
         <is>
           <t>Tên đợt thanh toán</t>
         </is>
       </c>
-      <c r="C13" s="37" t="inlineStr">
+      <c r="C13" s="40" t="inlineStr">
         <is>
           <t>Hợp đồng</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="40" t="inlineStr">
         <is>
           <t>Dự án / Gói thầu</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="40" t="inlineStr">
         <is>
           <t>Tỷ lệ (%)</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
+      <c r="F13" s="40" t="inlineStr">
         <is>
           <t>Giá trị thanh toán</t>
         </is>
       </c>
-      <c r="G13" s="37" t="inlineStr">
+      <c r="G13" s="40" t="inlineStr">
         <is>
           <t>Hạn thanh toán</t>
         </is>
       </c>
-      <c r="H13" s="37" t="inlineStr">
+      <c r="H13" s="40" t="inlineStr">
         <is>
           <t>Tình trạng hồ sơ nghiệm thu</t>
         </is>
       </c>
-      <c r="I13" s="37" t="inlineStr">
+      <c r="I13" s="40" t="inlineStr">
         <is>
           <t>Trạng thái thanh toán</t>
         </is>
       </c>
-      <c r="J13" s="37" t="inlineStr">
+      <c r="J13" s="40" t="inlineStr">
         <is>
           <t>Giá trị HĐ còn lại chưa trả</t>
         </is>
@@ -4785,7 +5235,7 @@
       <c r="A14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B14" s="39" t="inlineStr">
+      <c r="B14" s="42" t="inlineStr">
         <is>
           <t>TT-HD001-01 (Tạm ứng 40%)</t>
         </is>
@@ -4805,7 +5255,7 @@
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F14" s="29" t="inlineStr">
+      <c r="F14" s="31" t="inlineStr">
         <is>
           <t>200.000.000</t>
         </is>
@@ -4820,12 +5270,12 @@
           <t>Đã nhận Thư bảo lãnh tạm ứng</t>
         </is>
       </c>
-      <c r="I14" s="40" t="inlineStr">
+      <c r="I14" s="43" t="inlineStr">
         <is>
           <t>🟢 Đã thanh toán</t>
         </is>
       </c>
-      <c r="J14" s="29" t="inlineStr">
+      <c r="J14" s="31" t="inlineStr">
         <is>
           <t>300.000.000</t>
         </is>
@@ -4835,7 +5285,7 @@
       <c r="A15" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B15" s="39" t="inlineStr">
+      <c r="B15" s="42" t="inlineStr">
         <is>
           <t>TT-HD001-02 (Nghiệm thu đợt 1)</t>
         </is>
@@ -4855,7 +5305,7 @@
           <t>40.0%</t>
         </is>
       </c>
-      <c r="F15" s="29" t="inlineStr">
+      <c r="F15" s="31" t="inlineStr">
         <is>
           <t>200.000.000</t>
         </is>
@@ -4870,12 +5320,12 @@
           <t>Đã ký Biên bản nghiệm thu bàn giao</t>
         </is>
       </c>
-      <c r="I15" s="41" t="inlineStr">
+      <c r="I15" s="44" t="inlineStr">
         <is>
           <t>🟡 Chưa thanh toán</t>
         </is>
       </c>
-      <c r="J15" s="29" t="inlineStr">
+      <c r="J15" s="31" t="inlineStr">
         <is>
           <t>100.000.000</t>
         </is>
@@ -4885,7 +5335,7 @@
       <c r="A16" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B16" s="39" t="inlineStr">
+      <c r="B16" s="42" t="inlineStr">
         <is>
           <t>TT-HD001-03 (Tất toán &amp; Bảo hành)</t>
         </is>
@@ -4905,7 +5355,7 @@
           <t>20.0%</t>
         </is>
       </c>
-      <c r="F16" s="29" t="inlineStr">
+      <c r="F16" s="31" t="inlineStr">
         <is>
           <t>100.000.000</t>
         </is>
@@ -4920,12 +5370,12 @@
           <t>Chờ hết thời hạn bảo hành</t>
         </is>
       </c>
-      <c r="I16" s="41" t="inlineStr">
+      <c r="I16" s="44" t="inlineStr">
         <is>
           <t>🟡 Chưa thanh toán</t>
         </is>
       </c>
-      <c r="J16" s="29" t="inlineStr">
+      <c r="J16" s="31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -5288,12 +5738,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S52"/>
+  <dimension ref="A1:S56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="45" customWidth="1" min="6" max="6"/>
@@ -5313,19 +5763,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="42" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>NGÂN HÀNG HỢP TÁC XÃ VIỆT NAM</t>
         </is>
       </c>
-      <c r="S1" s="43" t="inlineStr">
+      <c r="S1" s="46" t="inlineStr">
         <is>
           <t>Biểu số 02.A</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="42" t="inlineStr">
+      <c r="A2" s="45" t="inlineStr">
         <is>
           <t>TRUNG TÂM CÔNG NGHỆ THÔNG TIN</t>
         </is>
@@ -5333,21 +5783,21 @@
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="A4" s="44" t="inlineStr">
+      <c r="A4" s="47" t="inlineStr">
         <is>
           <t>TÌNH HÌNH ĐẦU TƯ VÀ HUY ĐỘNG VỐN ĐỂ ĐẦU TƯ VÀO CÁC DỰ ÁN HÌNH THÀNH TSCĐ VÀ XDCB</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="45" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
         <is>
           <t>(Ban hành kèm theo Thông tư số 200/2015/TT-BTC ngày 15/12/2015 của Bộ Tài chính)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="46" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>Kỳ báo cáo: Quý III năm 2026 | Đơn vị tính: Tỷ đồng</t>
         </is>
@@ -5355,22 +5805,22 @@
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="47" t="inlineStr">
+      <c r="A8" s="50" t="inlineStr">
         <is>
           <t>TT</t>
         </is>
       </c>
-      <c r="B8" s="47" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>Tên dự án</t>
         </is>
       </c>
-      <c r="C8" s="47" t="inlineStr">
+      <c r="C8" s="50" t="inlineStr">
         <is>
           <t>Quyết định phê duyệt</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>Tổng mức vốn đầu tư</t>
         </is>
@@ -5379,33 +5829,33 @@
       <c r="F8" s="23" t="n"/>
       <c r="G8" s="23" t="n"/>
       <c r="H8" s="23" t="n"/>
-      <c r="I8" s="47" t="inlineStr">
+      <c r="I8" s="50" t="inlineStr">
         <is>
           <t>Thời gian đầu tư theo KH</t>
         </is>
       </c>
-      <c r="J8" s="47" t="inlineStr">
+      <c r="J8" s="50" t="inlineStr">
         <is>
           <t>Nguồn vốn huy động</t>
         </is>
       </c>
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="23" t="n"/>
-      <c r="M8" s="47" t="inlineStr">
+      <c r="M8" s="50" t="inlineStr">
         <is>
           <t>Giá trị khối lượng thực hiện đến cuối kỳ</t>
         </is>
       </c>
       <c r="N8" s="23" t="n"/>
       <c r="O8" s="23" t="n"/>
-      <c r="P8" s="47" t="inlineStr">
+      <c r="P8" s="50" t="inlineStr">
         <is>
           <t>Giải ngân đến cuối kỳ</t>
         </is>
       </c>
       <c r="Q8" s="23" t="n"/>
       <c r="R8" s="23" t="n"/>
-      <c r="S8" s="47" t="inlineStr">
+      <c r="S8" s="50" t="inlineStr">
         <is>
           <t>Giá trị tài sản đã hình thành đưa vào sử dụng</t>
         </is>
@@ -5415,73 +5865,73 @@
       <c r="A9" s="23" t="n"/>
       <c r="B9" s="23" t="n"/>
       <c r="C9" s="23" t="n"/>
-      <c r="D9" s="48" t="inlineStr">
+      <c r="D9" s="29" t="inlineStr">
         <is>
           <t>Tổng</t>
         </is>
       </c>
-      <c r="E9" s="48" t="inlineStr">
+      <c r="E9" s="29" t="inlineStr">
         <is>
           <t>Vốn CSH</t>
         </is>
       </c>
-      <c r="F9" s="48" t="inlineStr">
+      <c r="F9" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="G9" s="48" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>Vốn vay/HĐ</t>
         </is>
       </c>
-      <c r="H9" s="48" t="inlineStr">
+      <c r="H9" s="29" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
       <c r="I9" s="23" t="n"/>
-      <c r="J9" s="48" t="inlineStr">
+      <c r="J9" s="29" t="inlineStr">
         <is>
           <t>Tổng số</t>
         </is>
       </c>
-      <c r="K9" s="48" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t>Thời hạn vay</t>
         </is>
       </c>
-      <c r="L9" s="48" t="inlineStr">
+      <c r="L9" s="29" t="inlineStr">
         <is>
           <t>Lãi suất (%)</t>
         </is>
       </c>
-      <c r="M9" s="48" t="inlineStr">
+      <c r="M9" s="29" t="inlineStr">
         <is>
           <t>Kỳ trước chuyển sang</t>
         </is>
       </c>
-      <c r="N9" s="48" t="inlineStr">
+      <c r="N9" s="29" t="inlineStr">
         <is>
           <t>Thực hiện trong kỳ</t>
         </is>
       </c>
-      <c r="O9" s="48" t="inlineStr">
+      <c r="O9" s="29" t="inlineStr">
         <is>
           <t>Lũy kế đến cuối kỳ</t>
         </is>
       </c>
-      <c r="P9" s="48" t="inlineStr">
+      <c r="P9" s="29" t="inlineStr">
         <is>
           <t>Kỳ trước chuyển sang</t>
         </is>
       </c>
-      <c r="Q9" s="48" t="inlineStr">
+      <c r="Q9" s="29" t="inlineStr">
         <is>
           <t>Thực hiện trong kỳ</t>
         </is>
       </c>
-      <c r="R9" s="48" t="inlineStr">
+      <c r="R9" s="29" t="inlineStr">
         <is>
           <t>Lũy kế đến cuối kỳ</t>
         </is>
@@ -5489,258 +5939,258 @@
       <c r="S9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>(1)</t>
         </is>
       </c>
-      <c r="B10" s="49" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>(2)</t>
         </is>
       </c>
-      <c r="C10" s="49" t="inlineStr">
+      <c r="C10" s="30" t="inlineStr">
         <is>
           <t>(3)</t>
         </is>
       </c>
-      <c r="D10" s="49" t="inlineStr">
+      <c r="D10" s="30" t="inlineStr">
         <is>
           <t>(4)</t>
         </is>
       </c>
-      <c r="E10" s="49" t="inlineStr">
+      <c r="E10" s="30" t="inlineStr">
         <is>
           <t>(5)</t>
         </is>
       </c>
-      <c r="F10" s="49" t="inlineStr">
+      <c r="F10" s="30" t="inlineStr">
         <is>
           <t>(6)</t>
         </is>
       </c>
-      <c r="G10" s="49" t="inlineStr">
+      <c r="G10" s="30" t="inlineStr">
         <is>
           <t>(7)</t>
         </is>
       </c>
-      <c r="H10" s="49" t="inlineStr">
+      <c r="H10" s="30" t="inlineStr">
         <is>
           <t>(8)</t>
         </is>
       </c>
-      <c r="I10" s="49" t="inlineStr">
+      <c r="I10" s="30" t="inlineStr">
         <is>
           <t>(9)</t>
         </is>
       </c>
-      <c r="J10" s="49" t="inlineStr">
+      <c r="J10" s="30" t="inlineStr">
         <is>
           <t>(10)</t>
         </is>
       </c>
-      <c r="K10" s="49" t="inlineStr">
+      <c r="K10" s="30" t="inlineStr">
         <is>
           <t>(11)</t>
         </is>
       </c>
-      <c r="L10" s="49" t="inlineStr">
+      <c r="L10" s="30" t="inlineStr">
         <is>
           <t>(12)</t>
         </is>
       </c>
-      <c r="M10" s="49" t="inlineStr">
+      <c r="M10" s="30" t="inlineStr">
         <is>
           <t>(13)</t>
         </is>
       </c>
-      <c r="N10" s="49" t="inlineStr">
+      <c r="N10" s="30" t="inlineStr">
         <is>
           <t>(14)</t>
         </is>
       </c>
-      <c r="O10" s="49" t="inlineStr">
+      <c r="O10" s="30" t="inlineStr">
         <is>
           <t>(15)</t>
         </is>
       </c>
-      <c r="P10" s="49" t="inlineStr">
+      <c r="P10" s="30" t="inlineStr">
         <is>
           <t>(16)</t>
         </is>
       </c>
-      <c r="Q10" s="49" t="inlineStr">
+      <c r="Q10" s="30" t="inlineStr">
         <is>
           <t>(17)</t>
         </is>
       </c>
-      <c r="R10" s="49" t="inlineStr">
+      <c r="R10" s="30" t="inlineStr">
         <is>
           <t>(18)</t>
         </is>
       </c>
-      <c r="S10" s="49" t="inlineStr">
+      <c r="S10" s="30" t="inlineStr">
         <is>
           <t>(19)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Các dự án nhóm A (Tổng mức vốn &gt; 800 tỷ đồng)</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr"/>
-      <c r="D11" s="11" t="inlineStr"/>
-      <c r="E11" s="11" t="inlineStr"/>
-      <c r="F11" s="11" t="inlineStr"/>
-      <c r="G11" s="11" t="inlineStr"/>
-      <c r="H11" s="11" t="inlineStr"/>
-      <c r="I11" s="10" t="inlineStr"/>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="11" t="inlineStr"/>
-      <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="11" t="inlineStr"/>
-      <c r="N11" s="11" t="inlineStr"/>
-      <c r="O11" s="11" t="inlineStr"/>
-      <c r="P11" s="11" t="inlineStr"/>
-      <c r="Q11" s="11" t="inlineStr"/>
-      <c r="R11" s="11" t="inlineStr"/>
-      <c r="S11" s="11" t="inlineStr"/>
+      <c r="B11" s="52" t="inlineStr">
+        <is>
+          <t>PHẦN A: CÁC DỰ ÁN CÓ QUYẾT ĐỊNH THÀNH LẬP TRƯỚC KỲ BÁO CÁO</t>
+        </is>
+      </c>
+      <c r="C11" s="52" t="inlineStr"/>
+      <c r="D11" s="52" t="inlineStr"/>
+      <c r="E11" s="52" t="inlineStr"/>
+      <c r="F11" s="52" t="inlineStr"/>
+      <c r="G11" s="52" t="inlineStr"/>
+      <c r="H11" s="52" t="inlineStr"/>
+      <c r="I11" s="51" t="inlineStr"/>
+      <c r="J11" s="52" t="inlineStr"/>
+      <c r="K11" s="52" t="inlineStr"/>
+      <c r="L11" s="52" t="inlineStr"/>
+      <c r="M11" s="52" t="inlineStr"/>
+      <c r="N11" s="52" t="inlineStr"/>
+      <c r="O11" s="52" t="inlineStr"/>
+      <c r="P11" s="52" t="inlineStr"/>
+      <c r="Q11" s="52" t="inlineStr"/>
+      <c r="R11" s="52" t="inlineStr"/>
+      <c r="S11" s="52" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr"/>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>Nhóm A (Tổng mức đầu tư &gt; 800 tỷ đồng)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr"/>
+      <c r="D12" s="11" t="inlineStr"/>
+      <c r="E12" s="11" t="inlineStr"/>
+      <c r="F12" s="11" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr"/>
+      <c r="H12" s="11" t="inlineStr"/>
+      <c r="I12" s="10" t="inlineStr"/>
+      <c r="J12" s="11" t="inlineStr"/>
+      <c r="K12" s="11" t="inlineStr"/>
+      <c r="L12" s="11" t="inlineStr"/>
+      <c r="M12" s="11" t="inlineStr"/>
+      <c r="N12" s="11" t="inlineStr"/>
+      <c r="O12" s="11" t="inlineStr"/>
+      <c r="P12" s="11" t="inlineStr"/>
+      <c r="Q12" s="11" t="inlineStr"/>
+      <c r="R12" s="11" t="inlineStr"/>
+      <c r="S12" s="11" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr"/>
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>(Không có)</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr"/>
-      <c r="D12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr"/>
+      <c r="D13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E12" s="8" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G12" s="8" t="inlineStr">
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H12" s="8" t="inlineStr">
+      <c r="H13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K12" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L12" s="8" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="B13" s="11" t="inlineStr">
-        <is>
-          <t>Các dự án nhóm B (Tổng mức vốn từ 45 đến 800 tỷ đồng)</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr"/>
-      <c r="D13" s="11" t="inlineStr"/>
-      <c r="E13" s="11" t="inlineStr"/>
-      <c r="F13" s="11" t="inlineStr"/>
-      <c r="G13" s="11" t="inlineStr"/>
-      <c r="H13" s="11" t="inlineStr"/>
-      <c r="I13" s="10" t="inlineStr"/>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="11" t="inlineStr"/>
-      <c r="L13" s="11" t="inlineStr"/>
-      <c r="M13" s="11" t="inlineStr"/>
-      <c r="N13" s="11" t="inlineStr"/>
-      <c r="O13" s="11" t="inlineStr"/>
-      <c r="P13" s="11" t="inlineStr"/>
-      <c r="Q13" s="11" t="inlineStr"/>
-      <c r="R13" s="11" t="inlineStr"/>
-      <c r="S13" s="11" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>I</t>
+          <t>II</t>
         </is>
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Dự án đầu tư xây dựng</t>
+          <t>Nhóm B (Tổng mức đầu tư từ 45 đến 800 tỷ đồng)</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr"/>
@@ -5765,149 +6215,127 @@
       <c r="A15" s="9" t="inlineStr"/>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>(Không có)</t>
+          <t>2. Dự án Công nghệ thông tin</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr"/>
-      <c r="D15" s="8" t="inlineStr">
+      <c r="D15" s="8" t="inlineStr"/>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="8" t="inlineStr"/>
+      <c r="K15" s="8" t="inlineStr"/>
+      <c r="L15" s="8" t="inlineStr"/>
+      <c r="M15" s="8" t="inlineStr"/>
+      <c r="N15" s="8" t="inlineStr"/>
+      <c r="O15" s="8" t="inlineStr"/>
+      <c r="P15" s="8" t="inlineStr"/>
+      <c r="Q15" s="8" t="inlineStr"/>
+      <c r="R15" s="8" t="inlineStr"/>
+      <c r="S15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>Triển khai xây dựng hệ thống dự phòng thảm họa tại NHHT</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>452/QĐ-NHHT ngày 12/08/2024</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>124.49</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>124.49</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G16" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>2025-2027</t>
+        </is>
+      </c>
+      <c r="J16" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S15" s="8" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>II</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Dự án công nghệ thông tin</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr"/>
-      <c r="F16" s="11" t="inlineStr"/>
-      <c r="G16" s="11" t="inlineStr"/>
-      <c r="H16" s="11" t="inlineStr"/>
-      <c r="I16" s="10" t="inlineStr"/>
-      <c r="J16" s="11" t="inlineStr"/>
-      <c r="K16" s="11" t="inlineStr"/>
-      <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="11" t="inlineStr"/>
-      <c r="N16" s="11" t="inlineStr"/>
-      <c r="O16" s="11" t="inlineStr"/>
-      <c r="P16" s="11" t="inlineStr"/>
-      <c r="Q16" s="11" t="inlineStr"/>
-      <c r="R16" s="11" t="inlineStr"/>
-      <c r="S16" s="11" t="inlineStr"/>
+      <c r="M16" s="31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="N16" s="31" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="O16" s="31" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="P16" s="31" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Q16" s="31" t="n">
+        <v>32.29</v>
+      </c>
+      <c r="R16" s="31" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="S16" s="31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Triển khai xây dựng hệ thống dự phòng thảm họa tại NHHT</t>
+          <t>Triển khai giải pháp quản trị tín dụng tập trung tại Ngân hàng Hợp tác</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Số: 452/QĐ-NHHT ngày 12/08/2024</t>
-        </is>
-      </c>
-      <c r="D17" s="29" t="n">
-        <v>124.49</v>
-      </c>
-      <c r="E17" s="29" t="n">
-        <v>124.49</v>
-      </c>
-      <c r="F17" s="29" t="n">
+          <t>793/QĐ-NHHT ngày 19/12/2025</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="E17" s="31" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="F17" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="G17" s="29" t="n">
+      <c r="G17" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H17" s="29" t="n">
+      <c r="H17" s="31" t="n">
         <v>0</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
@@ -5915,7 +6343,7 @@
           <t>2025-2027</t>
         </is>
       </c>
-      <c r="J17" s="29" t="n">
+      <c r="J17" s="31" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="8" t="inlineStr">
@@ -5928,1074 +6356,1080 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M17" s="29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="N17" s="29" t="n">
-        <v>32.29</v>
-      </c>
-      <c r="O17" s="29" t="n">
-        <v>33.76</v>
-      </c>
-      <c r="P17" s="29" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Q17" s="29" t="n">
-        <v>32.29</v>
-      </c>
-      <c r="R17" s="29" t="n">
-        <v>33.76</v>
-      </c>
-      <c r="S17" s="29" t="n">
+      <c r="M17" s="31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N17" s="31" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="O17" s="31" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="P17" s="31" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="Q17" s="31" t="n">
+        <v>16.49</v>
+      </c>
+      <c r="R17" s="31" t="n">
+        <v>17.33</v>
+      </c>
+      <c r="S17" s="31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B18" s="8" t="inlineStr">
-        <is>
-          <t>Triển khai giải pháp quản trị tín dụng tập trung tại Ngân hàng Hợp tác</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>793/QĐ-NHHT ngày 19/12/2025</t>
-        </is>
-      </c>
-      <c r="D18" s="29" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="E18" s="29" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="F18" s="29" t="n">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
+      <c r="B18" s="11" t="inlineStr">
+        <is>
+          <t>Nhóm C (Tổng mức đầu tư &lt; 45 tỷ đồng)</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr"/>
+      <c r="D18" s="11" t="inlineStr"/>
+      <c r="E18" s="11" t="inlineStr"/>
+      <c r="F18" s="11" t="inlineStr"/>
+      <c r="G18" s="11" t="inlineStr"/>
+      <c r="H18" s="11" t="inlineStr"/>
+      <c r="I18" s="10" t="inlineStr"/>
+      <c r="J18" s="11" t="inlineStr"/>
+      <c r="K18" s="11" t="inlineStr"/>
+      <c r="L18" s="11" t="inlineStr"/>
+      <c r="M18" s="11" t="inlineStr"/>
+      <c r="N18" s="11" t="inlineStr"/>
+      <c r="O18" s="11" t="inlineStr"/>
+      <c r="P18" s="11" t="inlineStr"/>
+      <c r="Q18" s="11" t="inlineStr"/>
+      <c r="R18" s="11" t="inlineStr"/>
+      <c r="S18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr"/>
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>2. Dự án Công nghệ thông tin</t>
+        </is>
+      </c>
+      <c r="C19" s="8" t="inlineStr"/>
+      <c r="D19" s="8" t="inlineStr"/>
+      <c r="E19" s="8" t="inlineStr"/>
+      <c r="F19" s="8" t="inlineStr"/>
+      <c r="G19" s="8" t="inlineStr"/>
+      <c r="H19" s="8" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="8" t="inlineStr"/>
+      <c r="K19" s="8" t="inlineStr"/>
+      <c r="L19" s="8" t="inlineStr"/>
+      <c r="M19" s="8" t="inlineStr"/>
+      <c r="N19" s="8" t="inlineStr"/>
+      <c r="O19" s="8" t="inlineStr"/>
+      <c r="P19" s="8" t="inlineStr"/>
+      <c r="Q19" s="8" t="inlineStr"/>
+      <c r="R19" s="8" t="inlineStr"/>
+      <c r="S19" s="8" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>Thay thế hệ thống mạng và bảo mật tại Trụ sở chính NHHT</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>378/QĐ-NHHT ngày 18/08/2025</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="E20" s="31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="F20" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="G18" s="29" t="n">
+      <c r="G20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="29" t="n">
+      <c r="H20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>2025-2027</t>
-        </is>
-      </c>
-      <c r="J18" s="29" t="n">
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>270 ngày</t>
+        </is>
+      </c>
+      <c r="J20" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="K18" s="8" t="inlineStr">
+      <c r="K20" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L18" s="8" t="inlineStr">
+      <c r="L20" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M18" s="29" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="N18" s="29" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="O18" s="29" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="P18" s="29" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="Q18" s="29" t="n">
-        <v>16.49</v>
-      </c>
-      <c r="R18" s="29" t="n">
-        <v>17.33</v>
-      </c>
-      <c r="S18" s="29" t="n">
+      <c r="M20" s="31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="N20" s="31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O20" s="31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="P20" s="31" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Q20" s="31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R20" s="31" t="n">
+        <v>4.77</v>
+      </c>
+      <c r="S20" s="31" t="n">
+        <v>4.77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Triển khai xây dựng kho dữ liệu tập trung (Data Warehouse)</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>410/QĐ-NHHT ngày 08/09/2025</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="E21" s="31" t="n">
+        <v>38.14</v>
+      </c>
+      <c r="F21" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" s="31" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr"/>
-      <c r="B19" s="11" t="inlineStr">
-        <is>
-          <t>Tổng cộng Nhóm B</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr"/>
-      <c r="D19" s="50" t="n">
-        <v>181.89</v>
-      </c>
-      <c r="E19" s="50" t="n">
-        <v>181.89</v>
-      </c>
-      <c r="F19" s="50" t="n">
+      <c r="H21" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>14 tháng</t>
+        </is>
+      </c>
+      <c r="J21" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L21" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" s="31" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="N21" s="31" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="O21" s="31" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="P21" s="31" t="n">
+        <v>11.63</v>
+      </c>
+      <c r="Q21" s="31" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="R21" s="31" t="n">
+        <v>27.21</v>
+      </c>
+      <c r="S21" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>Xây dựng hệ thống đào tạo trực tuyến E-learning</t>
+        </is>
+      </c>
+      <c r="C22" s="8" t="inlineStr">
+        <is>
+          <t>481/QĐ-NHHT ngày 15/10/2025</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="E22" s="31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F22" s="31" t="n">
         <v>100</v>
       </c>
-      <c r="G19" s="50" t="n">
+      <c r="G22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="H19" s="50" t="n">
+      <c r="H22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I19" s="10" t="inlineStr"/>
-      <c r="J19" s="50" t="n">
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>14 tháng</t>
+        </is>
+      </c>
+      <c r="J22" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="K19" s="11" t="inlineStr">
+      <c r="K22" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L19" s="11" t="inlineStr">
+      <c r="L22" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M19" s="50" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="N19" s="50" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="O19" s="50" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="P19" s="50" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="Q19" s="50" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="R19" s="50" t="n">
-        <v>51.09</v>
-      </c>
-      <c r="S19" s="50" t="n">
+      <c r="M22" s="31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N22" s="31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="O22" s="31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="P22" s="31" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q22" s="31" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="R22" s="31" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="S22" s="31" t="n">
+        <v>0.98</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="53" t="inlineStr"/>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>Cộng PHẦN A</t>
+        </is>
+      </c>
+      <c r="C23" s="54" t="inlineStr"/>
+      <c r="D23" s="55" t="n">
+        <v>227.76</v>
+      </c>
+      <c r="E23" s="55" t="n">
+        <v>227.76</v>
+      </c>
+      <c r="F23" s="55" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="55" t="n">
         <v>0</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="B20" s="11" t="inlineStr">
-        <is>
-          <t>Các dự án khác / Nhóm C (Tổng mức vốn &lt; 45 tỷ đồng)</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr"/>
-      <c r="D20" s="11" t="inlineStr"/>
-      <c r="E20" s="11" t="inlineStr"/>
-      <c r="F20" s="11" t="inlineStr"/>
-      <c r="G20" s="11" t="inlineStr"/>
-      <c r="H20" s="11" t="inlineStr"/>
-      <c r="I20" s="10" t="inlineStr"/>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="11" t="inlineStr"/>
-      <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="11" t="inlineStr"/>
-      <c r="N20" s="11" t="inlineStr"/>
-      <c r="O20" s="11" t="inlineStr"/>
-      <c r="P20" s="11" t="inlineStr"/>
-      <c r="Q20" s="11" t="inlineStr"/>
-      <c r="R20" s="11" t="inlineStr"/>
-      <c r="S20" s="11" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="10" t="inlineStr">
+      <c r="H23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="53" t="inlineStr"/>
+      <c r="J23" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" s="55" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="N23" s="55" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="O23" s="55" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="P23" s="55" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="Q23" s="55" t="n">
+        <v>68.45999999999999</v>
+      </c>
+      <c r="R23" s="55" t="n">
+        <v>86.02</v>
+      </c>
+      <c r="S23" s="55" t="n">
+        <v>5.75</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B24" s="52" t="inlineStr">
+        <is>
+          <t>PHẦN B: CÁC DỰ ÁN CÓ QUYẾT ĐỊNH THÀNH LẬP TRONG KỲ BÁO CÁO</t>
+        </is>
+      </c>
+      <c r="C24" s="52" t="inlineStr"/>
+      <c r="D24" s="52" t="inlineStr"/>
+      <c r="E24" s="52" t="inlineStr"/>
+      <c r="F24" s="52" t="inlineStr"/>
+      <c r="G24" s="52" t="inlineStr"/>
+      <c r="H24" s="52" t="inlineStr"/>
+      <c r="I24" s="51" t="inlineStr"/>
+      <c r="J24" s="52" t="inlineStr"/>
+      <c r="K24" s="52" t="inlineStr"/>
+      <c r="L24" s="52" t="inlineStr"/>
+      <c r="M24" s="52" t="inlineStr"/>
+      <c r="N24" s="52" t="inlineStr"/>
+      <c r="O24" s="52" t="inlineStr"/>
+      <c r="P24" s="52" t="inlineStr"/>
+      <c r="Q24" s="52" t="inlineStr"/>
+      <c r="R24" s="52" t="inlineStr"/>
+      <c r="S24" s="52" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>I</t>
         </is>
       </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Dự án đầu tư xây dựng</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr"/>
-      <c r="D21" s="11" t="inlineStr"/>
-      <c r="E21" s="11" t="inlineStr"/>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="10" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr"/>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr"/>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr"/>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>Nhóm A (Tổng mức đầu tư &gt; 800 tỷ đồng)</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr"/>
+      <c r="D25" s="11" t="inlineStr"/>
+      <c r="E25" s="11" t="inlineStr"/>
+      <c r="F25" s="11" t="inlineStr"/>
+      <c r="G25" s="11" t="inlineStr"/>
+      <c r="H25" s="11" t="inlineStr"/>
+      <c r="I25" s="10" t="inlineStr"/>
+      <c r="J25" s="11" t="inlineStr"/>
+      <c r="K25" s="11" t="inlineStr"/>
+      <c r="L25" s="11" t="inlineStr"/>
+      <c r="M25" s="11" t="inlineStr"/>
+      <c r="N25" s="11" t="inlineStr"/>
+      <c r="O25" s="11" t="inlineStr"/>
+      <c r="P25" s="11" t="inlineStr"/>
+      <c r="Q25" s="11" t="inlineStr"/>
+      <c r="R25" s="11" t="inlineStr"/>
+      <c r="S25" s="11" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr"/>
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>(Không có)</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr"/>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="C26" s="8" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
+      <c r="E26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G22" s="8" t="inlineStr">
+      <c r="G26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H22" s="8" t="inlineStr">
+      <c r="H26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J22" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K22" s="8" t="inlineStr">
+      <c r="K26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="L26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M22" s="8" t="inlineStr">
+      <c r="M26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N22" s="8" t="inlineStr">
+      <c r="N26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="O22" s="8" t="inlineStr">
+      <c r="O26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P22" s="8" t="inlineStr">
+      <c r="P26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q22" s="8" t="inlineStr">
+      <c r="Q26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R22" s="8" t="inlineStr">
+      <c r="R26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S22" s="8" t="inlineStr">
+      <c r="S26" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="10" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
         <is>
           <t>II</t>
         </is>
       </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Dự án công nghệ thông tin</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr"/>
-      <c r="D23" s="11" t="inlineStr"/>
-      <c r="E23" s="11" t="inlineStr"/>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="10" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr"/>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr"/>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="inlineStr">
-        <is>
-          <t>Thay thế hệ thống mạng và bảo mật tại Trụ sở chính NHHT</t>
-        </is>
-      </c>
-      <c r="C24" s="8" t="inlineStr">
-        <is>
-          <t>378/QĐ-NHHT ngày 18/08/2025</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G24" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>270 ngày</t>
-        </is>
-      </c>
-      <c r="J24" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Nhóm B (Tổng mức đầu tư từ 45 đến 800 tỷ đồng)</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr"/>
+      <c r="D27" s="11" t="inlineStr"/>
+      <c r="E27" s="11" t="inlineStr"/>
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="10" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr"/>
+      <c r="N27" s="11" t="inlineStr"/>
+      <c r="O27" s="11" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
+      <c r="Q27" s="11" t="inlineStr"/>
+      <c r="R27" s="11" t="inlineStr"/>
+      <c r="S27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr"/>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>(Không có)</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr"/>
+      <c r="D28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L24" s="8" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M24" s="29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="N24" s="29" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O24" s="29" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="P24" s="29" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Q24" s="29" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R24" s="29" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="S24" s="29" t="n">
-        <v>4.77</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Triển khai xây dựng kho dữ liệu tập trung (Data Warehouse)</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>410/QĐ-NHHT ngày 08/09/2025</t>
-        </is>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>38.14</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>14 tháng</t>
-        </is>
-      </c>
-      <c r="J25" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="8" t="inlineStr">
+      <c r="F28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L25" s="8" t="inlineStr">
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M25" s="29" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="N25" s="29" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="O25" s="29" t="n">
-        <v>27.21</v>
-      </c>
-      <c r="P25" s="29" t="n">
-        <v>11.63</v>
-      </c>
-      <c r="Q25" s="29" t="n">
-        <v>15.58</v>
-      </c>
-      <c r="R25" s="29" t="n">
-        <v>27.21</v>
-      </c>
-      <c r="S25" s="29" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Xây dựng hệ thống đào tạo trực tuyến E-learning</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>481/QĐ-NHHT ngày 15/10/2025</t>
-        </is>
-      </c>
-      <c r="D26" s="29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="E26" s="29" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="F26" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>14 tháng</t>
-        </is>
-      </c>
-      <c r="J26" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="8" t="inlineStr">
+      <c r="H28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L26" s="8" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M26" s="29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="N26" s="29" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="O26" s="29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P26" s="29" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q26" s="29" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="R26" s="29" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="S26" s="29" t="n">
-        <v>0.98</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Xây dựng website mới Co-opBank</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>97/QĐ-NHHT ngày 06/02/2026</t>
-        </is>
-      </c>
-      <c r="D27" s="29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="E27" s="29" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="F27" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>8 tháng</t>
-        </is>
-      </c>
-      <c r="J27" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="8" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L27" s="8" t="inlineStr">
+      <c r="K28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M27" s="29" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="N27" s="29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O27" s="29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="P27" s="29" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="Q27" s="29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R27" s="29" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="S27" s="29" t="n">
-        <v>1.89</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Mua sắm hệ thống sao lưu và phục hồi dữ liệu</t>
-        </is>
-      </c>
-      <c r="C28" s="8" t="inlineStr">
-        <is>
-          <t>140/QĐ-NHHT ngày 03/03/2026</t>
-        </is>
-      </c>
-      <c r="D28" s="29" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="E28" s="29" t="n">
-        <v>24.83</v>
-      </c>
-      <c r="F28" s="29" t="n">
-        <v>100</v>
-      </c>
-      <c r="G28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>12 tháng</t>
-        </is>
-      </c>
-      <c r="J28" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="8" t="inlineStr">
+      <c r="L28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L28" s="8" t="inlineStr">
+      <c r="M28" s="8" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M28" s="29" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="N28" s="29" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O28" s="29" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="P28" s="29" t="n">
-        <v>7.41</v>
-      </c>
-      <c r="Q28" s="29" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="R28" s="29" t="n">
-        <v>7.52</v>
-      </c>
-      <c r="S28" s="29" t="n">
-        <v>0</v>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr"/>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>III</t>
+        </is>
+      </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Tổng cộng Nhóm C</t>
+          <t>Nhóm C (Tổng mức đầu tư &lt; 45 tỷ đồng)</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr"/>
-      <c r="D29" s="50" t="n">
-        <v>72.65000000000001</v>
-      </c>
-      <c r="E29" s="50" t="n">
-        <v>72.65000000000001</v>
-      </c>
-      <c r="F29" s="50" t="n">
-        <v>100</v>
-      </c>
-      <c r="G29" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="50" t="n">
-        <v>0</v>
-      </c>
+      <c r="D29" s="11" t="inlineStr"/>
+      <c r="E29" s="11" t="inlineStr"/>
+      <c r="F29" s="11" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="10" t="inlineStr"/>
-      <c r="J29" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L29" s="11" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M29" s="50" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="N29" s="50" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="O29" s="50" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="P29" s="50" t="n">
-        <v>23.26</v>
-      </c>
-      <c r="Q29" s="50" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="R29" s="50" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="S29" s="50" t="n">
-        <v>7.64</v>
-      </c>
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr"/>
+      <c r="L29" s="11" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr"/>
+      <c r="N29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
+      <c r="Q29" s="11" t="inlineStr"/>
+      <c r="R29" s="11" t="inlineStr"/>
+      <c r="S29" s="11" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr"/>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>TỔNG CỘNG TOÀN BỘ (A + B + C)</t>
+          <t>2. Dự án Công nghệ thông tin</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr"/>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="8" t="inlineStr"/>
+      <c r="E30" s="8" t="inlineStr"/>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr"/>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr"/>
+      <c r="K30" s="8" t="inlineStr"/>
+      <c r="L30" s="8" t="inlineStr"/>
+      <c r="M30" s="8" t="inlineStr"/>
+      <c r="N30" s="8" t="inlineStr"/>
+      <c r="O30" s="8" t="inlineStr"/>
+      <c r="P30" s="8" t="inlineStr"/>
+      <c r="Q30" s="8" t="inlineStr"/>
+      <c r="R30" s="8" t="inlineStr"/>
+      <c r="S30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>Xây dựng website mới Co-opBank</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>97/QĐ-NHHT ngày 06/02/2026</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="E31" s="31" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F31" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>8 tháng</t>
+        </is>
+      </c>
+      <c r="J31" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" s="31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="N31" s="31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="O31" s="31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="P31" s="31" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="Q31" s="31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R31" s="31" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="S31" s="31" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t>Mua sắm hệ thống sao lưu và phục hồi dữ liệu</t>
+        </is>
+      </c>
+      <c r="C32" s="8" t="inlineStr">
+        <is>
+          <t>140/QĐ-NHHT ngày 03/03/2026</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="E32" s="31" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="F32" s="31" t="n">
+        <v>100</v>
+      </c>
+      <c r="G32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>12 tháng</t>
+        </is>
+      </c>
+      <c r="J32" s="31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" s="31" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="N32" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="O32" s="31" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="P32" s="31" t="n">
+        <v>7.41</v>
+      </c>
+      <c r="Q32" s="31" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="R32" s="31" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="S32" s="31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="53" t="inlineStr"/>
+      <c r="B33" s="54" t="inlineStr">
+        <is>
+          <t>Cộng PHẦN B</t>
+        </is>
+      </c>
+      <c r="C33" s="54" t="inlineStr"/>
+      <c r="D33" s="55" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="E33" s="55" t="n">
+        <v>26.78</v>
+      </c>
+      <c r="F33" s="55" t="n">
+        <v>100</v>
+      </c>
+      <c r="G33" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="53" t="inlineStr"/>
+      <c r="J33" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L33" s="54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="N33" s="55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="O33" s="55" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="P33" s="55" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q33" s="55" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="R33" s="55" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="S33" s="55" t="n">
+        <v>1.89</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr"/>
+      <c r="B34" s="56" t="inlineStr">
+        <is>
+          <t>TỔNG CỘNG TOÀN BỘ (PHẦN A + PHẦN B)</t>
+        </is>
+      </c>
+      <c r="C34" s="56" t="inlineStr"/>
+      <c r="D34" s="32" t="n">
         <v>254.54</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E34" s="32" t="n">
         <v>254.54</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F34" s="32" t="n">
         <v>100</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="H30" s="29" t="n">
+      <c r="H34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="9" t="inlineStr"/>
-      <c r="J30" s="29" t="n">
+      <c r="I34" s="22" t="inlineStr"/>
+      <c r="J34" s="32" t="n">
         <v>0</v>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="K34" s="56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L30" s="8" t="inlineStr">
+      <c r="L34" s="56" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="M30" s="29" t="n">
+      <c r="M34" s="32" t="n">
         <v>25.58</v>
       </c>
-      <c r="N30" s="29" t="n">
+      <c r="N34" s="32" t="n">
         <v>69.88</v>
       </c>
-      <c r="O30" s="29" t="n">
+      <c r="O34" s="32" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="P30" s="29" t="n">
+      <c r="P34" s="32" t="n">
         <v>25.58</v>
       </c>
-      <c r="Q30" s="29" t="n">
+      <c r="Q34" s="32" t="n">
         <v>69.88</v>
       </c>
-      <c r="R30" s="29" t="n">
+      <c r="R34" s="32" t="n">
         <v>95.43000000000001</v>
       </c>
-      <c r="S30" s="29" t="n">
+      <c r="S34" s="32" t="n">
         <v>7.64</v>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="24" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>MÔ TẢ NGUỒN DỮ LIỆU 19 CỘT BIỂU 02.A TỪ DATABASE (DATA MAPPING)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>STT</t>
         </is>
       </c>
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B37" s="25" t="inlineStr">
         <is>
           <t>Tên Cột Hiển Thị Trên UI</t>
         </is>
       </c>
-      <c r="C33" s="25" t="inlineStr">
+      <c r="C37" s="25" t="inlineStr">
         <is>
           <t>Bảng / Entity Nguồn</t>
         </is>
       </c>
-      <c r="D33" s="25" t="inlineStr">
+      <c r="D37" s="25" t="inlineStr">
         <is>
           <t>Trường Dữ Liệu (Field)</t>
         </is>
       </c>
-      <c r="E33" s="25" t="inlineStr">
+      <c r="E37" s="25" t="inlineStr">
         <is>
           <t>Kiểu Dữ Liệu</t>
         </is>
       </c>
-      <c r="F33" s="25" t="inlineStr">
+      <c r="F37" s="25" t="inlineStr">
         <is>
           <t>Logic Lấy Dữ Liệu &amp; Công Thức Tính Toán Chi Tiết</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
-        <is>
-          <t>(1) TT</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="inlineStr">
-        <is>
-          <t>Chương trình (System)</t>
-        </is>
-      </c>
-      <c r="D34" s="12" t="inlineStr">
-        <is>
-          <t>STT / Group</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F34" s="12" t="inlineStr">
-        <is>
-          <t>Phân nhóm cấp 1: A, B, C; Phân loại cấp 2: I, II, III; STT dự án: 1, 2, 3...</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>(2) Tên dự án</t>
-        </is>
-      </c>
-      <c r="C35" s="8" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
-        </is>
-      </c>
-      <c r="D35" s="8" t="inlineStr">
-        <is>
-          <t>DuAn.Name</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>Tên đầy đủ của dự án đầu tư</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>(3) Quyết định phê duyệt</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
-        </is>
-      </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>DuAn.SoQuyetDinh</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F36" s="12" t="inlineStr">
-        <is>
-          <t>Số và ngày quyết định phê duyệt dự án/chủ trương đầu tư</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>(4) Tổng mức vốn đầu tư - Tổng</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>DuAn.DuToanPheDuyet</t>
-        </is>
-      </c>
-      <c r="E37" s="9" t="inlineStr">
-        <is>
-          <t>decimal</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>Tổng mức vốn đầu tư được phê duyệt của dự án (Tỷ đồng)</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>(5) Vốn chủ sở hữu</t>
+          <t>(1) TT</t>
         </is>
       </c>
       <c r="C38" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAnNguonVons</t>
+          <t>Chương trình (System)</t>
         </is>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
-          <t>Sum(DuAnNguonVon.GiaTri Where Loai == VCSH)</t>
+          <t>STT / Group</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
         <is>
-          <t>Vốn tự có / vốn chủ sở hữu phân bổ cho dự án</t>
+          <t>Phân khối: A (Trước kỳ), B (Trong kỳ); Phân nhóm: I, II, III; STT dự án: 1, 2, 3...</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>(6) % Vốn CSH</t>
+          <t>(2) Tên dự án</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng DuAns (Entity DuAn)</t>
         </is>
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>(Cột 5 / Cột 4) * 100</t>
+          <t>DuAn.Name</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>Tỷ lệ % vốn CSH trong tổng mức vốn đầu tư</t>
+          <t>Tên đầy đủ của dự án đầu tư (Chỉ lấy dự án ĐÃ CÓ QUYẾT ĐỊNH THÀNH LẬP)</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>(7) Vốn huy động / Vay</t>
+          <t>(3) Quyết định phê duyệt / Thành lập</t>
         </is>
       </c>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAnNguonVons</t>
+          <t>Bảng DuAns (Entity DuAn)</t>
         </is>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
-          <t>Sum(DuAnNguonVon.GiaTri Where Loai == Vay)</t>
+          <t>DuAn.SoQuyetDinhThanhLap / NgayQuyetDinhThanhLap</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>Vốn vay hoặc huy động hợp pháp khác</t>
+          <t>Số và ngày quyết định thành lập dự án (vd: '452/QĐ-NHHT ngày 12/08/2024')</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>(8) % Vốn huy động</t>
+          <t>(4) Tổng mức vốn đầu tư - Tổng</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng DuAns (Entity DuAn)</t>
         </is>
       </c>
       <c r="D41" s="8" t="inlineStr">
         <is>
-          <t>(Cột 7 / Cột 4) * 100</t>
+          <t>DuAn.DuToanPheDuyet</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -7005,57 +7439,57 @@
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>Tỷ lệ % vốn huy động trong tổng mức vốn đầu tư</t>
+          <t>Tổng mức vốn đầu tư được phê duyệt của dự án (Tỷ đồng)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>(9) Thời gian đầu tư theo KH</t>
+          <t>(5) Vốn chủ sở hữu</t>
         </is>
       </c>
       <c r="C42" s="12" t="inlineStr">
         <is>
-          <t>Bảng DuAns (Entity DuAn)</t>
+          <t>Bảng DuAnNguonVons</t>
         </is>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
-          <t>DuAn.ThoiGianThucHien / NamBatDau - NamKetThuc</t>
+          <t>Sum(DuAnNguonVon.GiaTri Where Loai == VCSH)</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
         <is>
-          <t>Thời gian triển khai theo kế hoạch (ví dụ: '2025-2027', '14 tháng', '270 ngày')</t>
+          <t>Vốn tự có / vốn chủ sở hữu phân bổ cho dự án</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>(10) Tổng số nguồn vốn vay</t>
+          <t>(6) % Vốn CSH</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAnNguonVons</t>
+          <t>Tính toán động</t>
         </is>
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>Sum(DuAnNguonVon.GiaTri Where Loai == Vay)</t>
+          <t>(Cột 5 / Cột 4) * 100</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -7065,17 +7499,17 @@
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>Tổng số vốn vay/huy động thực tế</t>
+          <t>Tỷ lệ % vốn CSH trong tổng mức vốn đầu tư</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>(11) Thời hạn vay</t>
+          <t>(7) Vốn huy động / Vay</t>
         </is>
       </c>
       <c r="C44" s="12" t="inlineStr">
@@ -7085,97 +7519,97 @@
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
-          <t>DuAnNguonVon.ThoiHanVay</t>
+          <t>Sum(DuAnNguonVon.GiaTri Where Loai == Vay)</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>Thời hạn của hợp đồng vay vốn (nếu có)</t>
+          <t>Vốn vay hoặc huy động hợp pháp khác</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>(12) Lãi suất (%)</t>
+          <t>(8) % Vốn huy động</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Bảng DuAnNguonVons</t>
+          <t>Tính toán động</t>
         </is>
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>DuAnNguonVon.LaiSuat</t>
+          <t>(Cột 7 / Cột 4) * 100</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
         <is>
-          <t>decimal?</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>Lãi suất tiền vay huy động theo năm (nếu có)</t>
+          <t>Tỷ lệ % vốn huy động trong tổng mức vốn đầu tư</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>(13) Khối lượng TH - Kỳ trước chuyển sang</t>
+          <t>(9) Thời gian đầu tư theo KH</t>
         </is>
       </c>
       <c r="C46" s="12" t="inlineStr">
         <is>
-          <t>Bảng DotThanhToans</t>
+          <t>Bảng DuAns (Entity DuAn)</t>
         </is>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
-          <t>DotThanhToan (IsPaid) có ngày &lt; Kỳ báo cáo</t>
+          <t>DuAn.ThoiGianThucHien / NamBatDau - NamKetThuc</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
         <is>
-          <t>Giá trị khối lượng nghiệm thu hoàn thành lũy kế từ khởi công đến trước ngày bắt đầu kỳ báo cáo</t>
+          <t>Thời gian triển khai theo kế hoạch (ví dụ: '2025-2027', '14 tháng', '270 ngày')</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>(14) Khối lượng TH - Thực hiện trong kỳ</t>
+          <t>(10) Tổng số nguồn vốn vay</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Bảng DotThanhToans</t>
+          <t>Bảng DuAnNguonVons</t>
         </is>
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>DotThanhToan (IsPaid) có ngày trong Kỳ báo cáo</t>
+          <t>Sum(DuAnNguonVon.GiaTri Where Loai == Vay)</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -7185,77 +7619,77 @@
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>Giá trị khối lượng nghiệm thu hoàn thành phát sinh trong kỳ báo cáo</t>
+          <t>Tổng số vốn vay/huy động thực tế</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="10" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>(15) Khối lượng TH - Lũy kế đến cuối kỳ</t>
+          <t>(11) Thời hạn vay</t>
         </is>
       </c>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng DuAnNguonVons</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>Cột 13 + Cột 14</t>
+          <t>DuAnNguonVon.ThoiHanVay</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>Tổng giá trị khối lượng thực hiện lũy kế đến thời điểm kết thúc kỳ báo cáo</t>
+          <t>Thời hạn của hợp đồng vay vốn (nếu có)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>(16) Giải ngân - Kỳ trước chuyển sang</t>
+          <t>(12) Lãi suất (%)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>Bảng DotThanhToans</t>
+          <t>Bảng DuAnNguonVons</t>
         </is>
       </c>
       <c r="D49" s="8" t="inlineStr">
         <is>
-          <t>DotThanhToan (IsPaid) có ngày &lt; Kỳ báo cáo</t>
+          <t>DuAnNguonVon.LaiSuat</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>decimal?</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>Số tiền vốn đã thanh toán/giải ngân lũy kế từ khởi công đến trước kỳ báo cáo</t>
+          <t>Lãi suất tiền vay huy động theo năm (nếu có)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="10" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>(17) Giải ngân - Thực hiện trong kỳ</t>
+          <t>(13) Khối lượng TH - Kỳ trước chuyển sang</t>
         </is>
       </c>
       <c r="C50" s="12" t="inlineStr">
@@ -7265,7 +7699,7 @@
       </c>
       <c r="D50" s="12" t="inlineStr">
         <is>
-          <t>DotThanhToan (IsPaid) có ngày trong Kỳ báo cáo</t>
+          <t>DotThanhToan (IsPaid) có ngày &lt; Kỳ báo cáo</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -7275,27 +7709,27 @@
       </c>
       <c r="F50" s="12" t="inlineStr">
         <is>
-          <t>Số tiền vốn đã thanh toán/giải ngân thực tế trong kỳ báo cáo</t>
+          <t>Giá trị khối lượng nghiệm thu hoàn thành lũy kế từ khởi công đến trước ngày bắt đầu kỳ báo cáo</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>(18) Giải ngân - Lũy kế đến cuối kỳ</t>
+          <t>(14) Khối lượng TH - Thực hiện trong kỳ</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>Tính toán động</t>
+          <t>Bảng DotThanhToans</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>Cột 16 + Cột 17</t>
+          <t>DotThanhToan (IsPaid) có ngày trong Kỳ báo cáo</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
@@ -7305,35 +7739,155 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>Tổng số tiền vốn đã giải ngân lũy kế đến cuối kỳ báo cáo</t>
+          <t>Giá trị khối lượng nghiệm thu hoàn thành phát sinh trong kỳ báo cáo</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>(15) Khối lượng TH - Lũy kế đến cuối kỳ</t>
+        </is>
+      </c>
+      <c r="C52" s="12" t="inlineStr">
+        <is>
+          <t>Tính toán động</t>
+        </is>
+      </c>
+      <c r="D52" s="12" t="inlineStr">
+        <is>
+          <t>Cột 13 + Cột 14</t>
+        </is>
+      </c>
+      <c r="E52" s="13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F52" s="12" t="inlineStr">
+        <is>
+          <t>Tổng giá trị khối lượng thực hiện lũy kế đến thời điểm kết thúc kỳ báo cáo</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>(16) Giải ngân - Kỳ trước chuyển sang</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="inlineStr">
+        <is>
+          <t>Bảng DotThanhToans</t>
+        </is>
+      </c>
+      <c r="D53" s="8" t="inlineStr">
+        <is>
+          <t>DotThanhToan (IsPaid) có ngày &lt; Kỳ báo cáo</t>
+        </is>
+      </c>
+      <c r="E53" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F53" s="8" t="inlineStr">
+        <is>
+          <t>Số tiền vốn đã thanh toán/giải ngân lũy kế từ khởi công đến trước kỳ báo cáo (Cột 16 = Cột 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>(17) Giải ngân - Thực hiện trong kỳ</t>
+        </is>
+      </c>
+      <c r="C54" s="12" t="inlineStr">
+        <is>
+          <t>Bảng DotThanhToans</t>
+        </is>
+      </c>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>DotThanhToan (IsPaid) có ngày trong Kỳ báo cáo</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F54" s="12" t="inlineStr">
+        <is>
+          <t>Số tiền vốn đã thanh toán/giải ngân thực tế trong kỳ báo cáo (Cột 17 = Cột 14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>(18) Giải ngân - Lũy kế đến cuối kỳ</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="inlineStr">
+        <is>
+          <t>Tính toán động</t>
+        </is>
+      </c>
+      <c r="D55" s="8" t="inlineStr">
+        <is>
+          <t>Cột 16 + Cột 17</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="F55" s="8" t="inlineStr">
+        <is>
+          <t>Tổng số tiền vốn đã giải ngân lũy kế đến cuối kỳ báo cáo (Cột 18 = Cột 15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="B52" s="11" t="inlineStr">
+      <c r="B56" s="11" t="inlineStr">
         <is>
           <t>(19) Giá trị tài sản đã hình thành đưa vào SD</t>
         </is>
       </c>
-      <c r="C52" s="12" t="inlineStr">
+      <c r="C56" s="12" t="inlineStr">
         <is>
           <t>Bảng DuAns / HopDongs</t>
         </is>
       </c>
-      <c r="D52" s="12" t="inlineStr">
+      <c r="D56" s="12" t="inlineStr">
         <is>
           <t>Sum(TaiSanBanGiao / NghiemThuTongThe)</t>
         </is>
       </c>
-      <c r="E52" s="13" t="inlineStr">
+      <c r="E56" s="13" t="inlineStr">
         <is>
           <t>decimal</t>
         </is>
       </c>
-      <c r="F52" s="12" t="inlineStr">
+      <c r="F56" s="12" t="inlineStr">
         <is>
           <t>Giá trị tài sản cố định đã hoàn thành đầu tư, nghiệm thu bàn giao và đưa vào sử dụng</t>
         </is>
@@ -7346,7 +7900,7 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="I8:I9"/>
     <mergeCell ref="P8:R8"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="B8:B9"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="S8:S9"/>
@@ -7403,7 +7957,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Đối Tượng Quản Lý</t>
+          <t>Đối TỢNG Quản Lý</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -7436,12 +7990,12 @@
           <t>Mã Dự án</t>
         </is>
       </c>
-      <c r="C6" s="51" t="inlineStr">
+      <c r="C6" s="57" t="inlineStr">
         <is>
           <t>DAN-[Năm]-[STT 3 số]</t>
         </is>
       </c>
-      <c r="D6" s="51" t="inlineStr">
+      <c r="D6" s="57" t="inlineStr">
         <is>
           <t>DAN-2026-214</t>
         </is>
@@ -7496,12 +8050,12 @@
           <t>Số / Mã Hợp đồng</t>
         </is>
       </c>
-      <c r="C8" s="51" t="inlineStr">
+      <c r="C8" s="57" t="inlineStr">
         <is>
           <t>HD-[Năm]-[STT 3 số]</t>
         </is>
       </c>
-      <c r="D8" s="51" t="inlineStr">
+      <c r="D8" s="57" t="inlineStr">
         <is>
           <t>HD-2026-017</t>
         </is>
@@ -7556,12 +8110,12 @@
           <t>Mã Nhà thầu / Đối tác</t>
         </is>
       </c>
-      <c r="C10" s="51" t="inlineStr">
+      <c r="C10" s="57" t="inlineStr">
         <is>
           <t>NT-[Tên viết tắt]</t>
         </is>
       </c>
-      <c r="D10" s="51" t="inlineStr">
+      <c r="D10" s="57" t="inlineStr">
         <is>
           <t>NT-CMC, NT-FPT</t>
         </is>
@@ -7616,12 +8170,12 @@
           <t>Mã Loại Dự án</t>
         </is>
       </c>
-      <c r="C12" s="51" t="inlineStr">
+      <c r="C12" s="57" t="inlineStr">
         <is>
           <t>LDA-[Tên viết tắt]</t>
         </is>
       </c>
-      <c r="D12" s="51" t="inlineStr">
+      <c r="D12" s="57" t="inlineStr">
         <is>
           <t>LDA-NHST, LDA-HT, LDA-XDCB</t>
         </is>
@@ -7702,7 +8256,7 @@
       <c r="A18" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="B18" s="51" t="inlineStr">
+      <c r="B18" s="57" t="inlineStr">
         <is>
           <t>PL_DIGITAL_BANKING</t>
         </is>
@@ -7742,7 +8296,7 @@
       <c r="A20" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B20" s="51" t="inlineStr">
+      <c r="B20" s="57" t="inlineStr">
         <is>
           <t>PL_XDCB</t>
         </is>
@@ -7782,7 +8336,7 @@
       <c r="A22" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="B22" s="51" t="inlineStr">
+      <c r="B22" s="57" t="inlineStr">
         <is>
           <t>PL_HTPM</t>
         </is>
@@ -7822,7 +8376,7 @@
       <c r="A24" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="B24" s="51" t="inlineStr">
+      <c r="B24" s="57" t="inlineStr">
         <is>
           <t>PL_MSHH_DV</t>
         </is>
